--- a/research/traditional_assets/database/data/greece/greece_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_office_equipment_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1047661409257655</v>
+        <v>0.1045707554157288</v>
       </c>
       <c r="C2">
-        <v>36.70740819750539</v>
+        <v>36.46783275968168</v>
       </c>
       <c r="D2">
-        <v>34.11740819750539</v>
+        <v>34.23083275968168</v>
       </c>
       <c r="E2">
-        <v>-24.2</v>
+        <v>-23.847</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="G2">
         <v>2.59</v>
@@ -1439,28 +1439,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0177559</v>
       </c>
       <c r="N2">
-        <v>4.926666666666668</v>
+        <v>4.908910766666668</v>
       </c>
       <c r="O2">
-        <v>1.083866666666667</v>
+        <v>1.079960368666667</v>
       </c>
       <c r="P2">
-        <v>3.8428</v>
+        <v>3.828950398000001</v>
       </c>
       <c r="Q2">
-        <v>5.902800000000001</v>
+        <v>5.888950398</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1047661409257655</v>
+        <v>0.1052307226421503</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431574</v>
+        <v>0.7745815457256187</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>277.4664571588412</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1045707554157288</v>
+        <v>0.1043753699056921</v>
       </c>
       <c r="C3">
-        <v>36.46783275968168</v>
+        <v>36.22901400563028</v>
       </c>
       <c r="D3">
-        <v>34.23083275968168</v>
+        <v>34.34501400563028</v>
       </c>
       <c r="E3">
-        <v>-23.847</v>
+        <v>-23.494</v>
       </c>
       <c r="F3">
-        <v>0.353</v>
+        <v>0.706</v>
       </c>
       <c r="G3">
         <v>2.59</v>
@@ -1521,28 +1521,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M3">
-        <v>0.0177559</v>
+        <v>0.0355118</v>
       </c>
       <c r="N3">
-        <v>4.908910766666668</v>
+        <v>4.891154866666668</v>
       </c>
       <c r="O3">
-        <v>1.079960368666667</v>
+        <v>1.076054070666667</v>
       </c>
       <c r="P3">
-        <v>3.828950398000001</v>
+        <v>3.815100796000001</v>
       </c>
       <c r="Q3">
-        <v>5.888950398</v>
+        <v>5.875100796000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1052307226421503</v>
+        <v>0.1057047856180532</v>
       </c>
       <c r="T3">
-        <v>0.7745815457256187</v>
+        <v>0.7807601755036403</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>277.4664571588412</v>
+        <v>138.7332285794206</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1043753699056921</v>
+        <v>0.1041799843956554</v>
       </c>
       <c r="C4">
-        <v>36.22901400563028</v>
+        <v>35.99095953273469</v>
       </c>
       <c r="D4">
-        <v>34.34501400563028</v>
+        <v>34.45995953273469</v>
       </c>
       <c r="E4">
-        <v>-23.494</v>
+        <v>-23.141</v>
       </c>
       <c r="F4">
-        <v>0.706</v>
+        <v>1.059</v>
       </c>
       <c r="G4">
         <v>2.59</v>
@@ -1603,28 +1603,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M4">
-        <v>0.0355118</v>
+        <v>0.05326769999999999</v>
       </c>
       <c r="N4">
-        <v>4.891154866666668</v>
+        <v>4.873398966666667</v>
       </c>
       <c r="O4">
-        <v>1.076054070666667</v>
+        <v>1.072147772666667</v>
       </c>
       <c r="P4">
-        <v>3.815100796000001</v>
+        <v>3.801251194000001</v>
       </c>
       <c r="Q4">
-        <v>5.875100796000001</v>
+        <v>5.861251194000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1057047856180532</v>
+        <v>0.1061886230883046</v>
       </c>
       <c r="T4">
-        <v>0.7807601755036403</v>
+        <v>0.7870661997100749</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>138.7332285794206</v>
+        <v>92.48881905294706</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1041799843956554</v>
+        <v>0.1039845988856187</v>
       </c>
       <c r="C5">
-        <v>35.99095953273469</v>
+        <v>35.75367704042745</v>
       </c>
       <c r="D5">
-        <v>34.45995953273469</v>
+        <v>34.57567704042746</v>
       </c>
       <c r="E5">
-        <v>-23.141</v>
+        <v>-22.788</v>
       </c>
       <c r="F5">
-        <v>1.059</v>
+        <v>1.412</v>
       </c>
       <c r="G5">
         <v>2.59</v>
@@ -1685,28 +1685,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M5">
-        <v>0.05326769999999999</v>
+        <v>0.07102359999999999</v>
       </c>
       <c r="N5">
-        <v>4.873398966666667</v>
+        <v>4.855643066666667</v>
       </c>
       <c r="O5">
-        <v>1.072147772666667</v>
+        <v>1.068241474666667</v>
       </c>
       <c r="P5">
-        <v>3.801251194000001</v>
+        <v>3.787401592000001</v>
       </c>
       <c r="Q5">
-        <v>5.861251194000001</v>
+        <v>5.847401592000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1061886230883046</v>
+        <v>0.1066825405058529</v>
       </c>
       <c r="T5">
-        <v>0.7870661997100749</v>
+        <v>0.7935035994208101</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>92.48881905294706</v>
+        <v>69.3666142897103</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1039845988856187</v>
+        <v>0.103789213375582</v>
       </c>
       <c r="C6">
-        <v>35.75367704042745</v>
+        <v>35.51717433190913</v>
       </c>
       <c r="D6">
-        <v>34.57567704042746</v>
+        <v>34.69217433190913</v>
       </c>
       <c r="E6">
-        <v>-22.788</v>
+        <v>-22.435</v>
       </c>
       <c r="F6">
-        <v>1.412</v>
+        <v>1.765</v>
       </c>
       <c r="G6">
         <v>2.59</v>
@@ -1767,28 +1767,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M6">
-        <v>0.07102359999999999</v>
+        <v>0.0887795</v>
       </c>
       <c r="N6">
-        <v>4.855643066666667</v>
+        <v>4.837887166666667</v>
       </c>
       <c r="O6">
-        <v>1.068241474666667</v>
+        <v>1.064335176666667</v>
       </c>
       <c r="P6">
-        <v>3.787401592000001</v>
+        <v>3.773551990000001</v>
       </c>
       <c r="Q6">
-        <v>5.847401592000001</v>
+        <v>5.83355199</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1066825405058529</v>
+        <v>0.1071868561848232</v>
       </c>
       <c r="T6">
-        <v>0.7935035994208101</v>
+        <v>0.8000765233359818</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.3666142897103</v>
+        <v>55.49329143176823</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.103789213375582</v>
+        <v>0.1035938278655454</v>
       </c>
       <c r="C7">
-        <v>35.51717433190913</v>
+        <v>35.2814593159024</v>
       </c>
       <c r="D7">
-        <v>34.69217433190913</v>
+        <v>34.80945931590241</v>
       </c>
       <c r="E7">
-        <v>-22.435</v>
+        <v>-22.082</v>
       </c>
       <c r="F7">
-        <v>1.765</v>
+        <v>2.118</v>
       </c>
       <c r="G7">
         <v>2.59</v>
@@ -1849,28 +1849,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M7">
-        <v>0.0887795</v>
+        <v>0.1065354</v>
       </c>
       <c r="N7">
-        <v>4.837887166666667</v>
+        <v>4.820131266666667</v>
       </c>
       <c r="O7">
-        <v>1.064335176666667</v>
+        <v>1.060428878666667</v>
       </c>
       <c r="P7">
-        <v>3.773551990000001</v>
+        <v>3.759702388</v>
       </c>
       <c r="Q7">
-        <v>5.83355199</v>
+        <v>5.819702388000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1071868561848232</v>
+        <v>0.1077019019846227</v>
       </c>
       <c r="T7">
-        <v>0.8000765233359818</v>
+        <v>0.8067892966961572</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.49329143176823</v>
+        <v>46.24440952647353</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1035938278655454</v>
+        <v>0.1033984423555087</v>
       </c>
       <c r="C8">
-        <v>35.2814593159024</v>
+        <v>35.04654000844199</v>
       </c>
       <c r="D8">
-        <v>34.80945931590241</v>
+        <v>34.92754000844198</v>
       </c>
       <c r="E8">
-        <v>-22.082</v>
+        <v>-21.729</v>
       </c>
       <c r="F8">
-        <v>2.118</v>
+        <v>2.471</v>
       </c>
       <c r="G8">
         <v>2.59</v>
@@ -1931,28 +1931,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M8">
-        <v>0.1065354</v>
+        <v>0.1242913</v>
       </c>
       <c r="N8">
-        <v>4.820131266666667</v>
+        <v>4.802375366666667</v>
       </c>
       <c r="O8">
-        <v>1.060428878666667</v>
+        <v>1.056522580666667</v>
       </c>
       <c r="P8">
-        <v>3.759702388</v>
+        <v>3.745852786</v>
       </c>
       <c r="Q8">
-        <v>5.819702388000001</v>
+        <v>5.805852786000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1077019019846227</v>
+        <v>0.1082280240381814</v>
       </c>
       <c r="T8">
-        <v>0.8067892966961572</v>
+        <v>0.8136464307737556</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.24440952647353</v>
+        <v>39.63806530840588</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1033984423555087</v>
+        <v>0.103203056845472</v>
       </c>
       <c r="C9">
-        <v>35.04654000844198</v>
+        <v>34.8124245347007</v>
       </c>
       <c r="D9">
-        <v>34.92754000844198</v>
+        <v>35.0464245347007</v>
       </c>
       <c r="E9">
-        <v>-21.729</v>
+        <v>-21.376</v>
       </c>
       <c r="F9">
-        <v>2.471</v>
+        <v>2.824</v>
       </c>
       <c r="G9">
         <v>2.59</v>
@@ -2013,28 +2013,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M9">
-        <v>0.1242913</v>
+        <v>0.1420472</v>
       </c>
       <c r="N9">
-        <v>4.802375366666667</v>
+        <v>4.784619466666667</v>
       </c>
       <c r="O9">
-        <v>1.056522580666667</v>
+        <v>1.052616282666667</v>
       </c>
       <c r="P9">
-        <v>3.745852786</v>
+        <v>3.732003184000001</v>
       </c>
       <c r="Q9">
-        <v>5.805852786000001</v>
+        <v>5.792003184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1082280240381814</v>
+        <v>0.1087655835276869</v>
       </c>
       <c r="T9">
-        <v>0.8136464307737558</v>
+        <v>0.8206526329834759</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.63806530840588</v>
+        <v>34.68330714485514</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.103203056845472</v>
+        <v>0.1030076713354353</v>
       </c>
       <c r="C10">
-        <v>34.8124245347007</v>
+        <v>34.5791211308534</v>
       </c>
       <c r="D10">
-        <v>35.0464245347007</v>
+        <v>35.1661211308534</v>
       </c>
       <c r="E10">
-        <v>-21.376</v>
+        <v>-21.023</v>
       </c>
       <c r="F10">
-        <v>2.824</v>
+        <v>3.177</v>
       </c>
       <c r="G10">
         <v>2.59</v>
@@ -2095,28 +2095,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M10">
-        <v>0.1420472</v>
+        <v>0.1598031</v>
       </c>
       <c r="N10">
-        <v>4.784619466666667</v>
+        <v>4.766863566666668</v>
       </c>
       <c r="O10">
-        <v>1.052616282666667</v>
+        <v>1.048709984666667</v>
       </c>
       <c r="P10">
-        <v>3.732003184000001</v>
+        <v>3.718153582000001</v>
       </c>
       <c r="Q10">
-        <v>5.792003184</v>
+        <v>5.778153582000002</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1087655835276869</v>
+        <v>0.1093149575114674</v>
       </c>
       <c r="T10">
-        <v>0.8206526329834759</v>
+        <v>0.8278128176593439</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.68330714485514</v>
+        <v>30.82960635098236</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1030076713354353</v>
+        <v>0.1028122858253986</v>
       </c>
       <c r="C11">
-        <v>34.5791211308534</v>
+        <v>34.34663814597899</v>
       </c>
       <c r="D11">
-        <v>35.1661211308534</v>
+        <v>35.28663814597899</v>
       </c>
       <c r="E11">
-        <v>-21.023</v>
+        <v>-20.67</v>
       </c>
       <c r="F11">
-        <v>3.177</v>
+        <v>3.529999999999999</v>
       </c>
       <c r="G11">
         <v>2.59</v>
@@ -2177,28 +2177,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M11">
-        <v>0.1598031</v>
+        <v>0.177559</v>
       </c>
       <c r="N11">
-        <v>4.766863566666668</v>
+        <v>4.749107666666668</v>
       </c>
       <c r="O11">
-        <v>1.048709984666667</v>
+        <v>1.044803686666667</v>
       </c>
       <c r="P11">
-        <v>3.718153582000001</v>
+        <v>3.704303980000001</v>
       </c>
       <c r="Q11">
-        <v>5.778153582000002</v>
+        <v>5.764303980000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1093149575114674</v>
+        <v>0.1098765398059985</v>
       </c>
       <c r="T11">
-        <v>0.8278128176593439</v>
+        <v>0.8351321175502311</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.82960635098236</v>
+        <v>27.74664571588412</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1028122858253986</v>
+        <v>0.102616900315362</v>
       </c>
       <c r="C12">
-        <v>34.34663814597899</v>
+        <v>34.11498404400165</v>
       </c>
       <c r="D12">
-        <v>35.28663814597899</v>
+        <v>35.40798404400165</v>
       </c>
       <c r="E12">
-        <v>-20.67</v>
+        <v>-20.317</v>
       </c>
       <c r="F12">
-        <v>3.53</v>
+        <v>3.883</v>
       </c>
       <c r="G12">
         <v>2.59</v>
@@ -2259,28 +2259,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M12">
-        <v>0.177559</v>
+        <v>0.1953149</v>
       </c>
       <c r="N12">
-        <v>4.749107666666668</v>
+        <v>4.731351766666668</v>
       </c>
       <c r="O12">
-        <v>1.044803686666667</v>
+        <v>1.040897388666667</v>
       </c>
       <c r="P12">
-        <v>3.704303980000001</v>
+        <v>3.690454378000001</v>
       </c>
       <c r="Q12">
-        <v>5.764303980000001</v>
+        <v>5.750454378000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1098765398059985</v>
+        <v>0.110450741927373</v>
       </c>
       <c r="T12">
-        <v>0.8351321175502311</v>
+        <v>0.8426158960903518</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.74664571588412</v>
+        <v>25.22422337807648</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.102616900315362</v>
+        <v>0.1024215148053253</v>
       </c>
       <c r="C13">
-        <v>34.11498404400165</v>
+        <v>33.88416740567246</v>
       </c>
       <c r="D13">
-        <v>35.40798404400165</v>
+        <v>35.53016740567246</v>
       </c>
       <c r="E13">
-        <v>-20.317</v>
+        <v>-19.964</v>
       </c>
       <c r="F13">
-        <v>3.883</v>
+        <v>4.236</v>
       </c>
       <c r="G13">
         <v>2.59</v>
@@ -2341,28 +2341,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M13">
-        <v>0.1953149</v>
+        <v>0.2130708</v>
       </c>
       <c r="N13">
-        <v>4.731351766666668</v>
+        <v>4.713595866666668</v>
       </c>
       <c r="O13">
-        <v>1.040897388666667</v>
+        <v>1.036991090666667</v>
       </c>
       <c r="P13">
-        <v>3.690454378000001</v>
+        <v>3.676604776000001</v>
       </c>
       <c r="Q13">
-        <v>5.750454378000001</v>
+        <v>5.736604776000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.110450741927373</v>
+        <v>0.1110379940969606</v>
       </c>
       <c r="T13">
-        <v>0.8426158960903518</v>
+        <v>0.8502697605063843</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.22422337807648</v>
+        <v>23.12220476323677</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1024215148053253</v>
+        <v>0.1022261292952886</v>
       </c>
       <c r="C14">
-        <v>33.88416740567246</v>
+        <v>33.65419693059197</v>
       </c>
       <c r="D14">
-        <v>35.53016740567246</v>
+        <v>35.65319693059197</v>
       </c>
       <c r="E14">
-        <v>-19.964</v>
+        <v>-19.611</v>
       </c>
       <c r="F14">
-        <v>4.236</v>
+        <v>4.589</v>
       </c>
       <c r="G14">
         <v>2.59</v>
@@ -2423,28 +2423,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M14">
-        <v>0.2130708</v>
+        <v>0.2308267</v>
       </c>
       <c r="N14">
-        <v>4.713595866666668</v>
+        <v>4.695839966666668</v>
       </c>
       <c r="O14">
-        <v>1.036991090666667</v>
+        <v>1.033084792666667</v>
       </c>
       <c r="P14">
-        <v>3.676604776000001</v>
+        <v>3.662755174000001</v>
       </c>
       <c r="Q14">
-        <v>5.736604776000001</v>
+        <v>5.722755174000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1110379940969606</v>
+        <v>0.1116387463164237</v>
       </c>
       <c r="T14">
-        <v>0.8502697605063843</v>
+        <v>0.8580995758285324</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.12220476323677</v>
+        <v>21.34357362760317</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1022261292952886</v>
+        <v>0.1020307437852519</v>
       </c>
       <c r="C15">
-        <v>33.65419693059197</v>
+        <v>33.4250814392751</v>
       </c>
       <c r="D15">
-        <v>35.65319693059197</v>
+        <v>35.77708143927509</v>
       </c>
       <c r="E15">
-        <v>-19.611</v>
+        <v>-19.258</v>
       </c>
       <c r="F15">
-        <v>4.589</v>
+        <v>4.942</v>
       </c>
       <c r="G15">
         <v>2.59</v>
@@ -2505,28 +2505,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M15">
-        <v>0.2308267</v>
+        <v>0.2485826</v>
       </c>
       <c r="N15">
-        <v>4.695839966666668</v>
+        <v>4.678084066666668</v>
       </c>
       <c r="O15">
-        <v>1.033084792666667</v>
+        <v>1.029178494666667</v>
       </c>
       <c r="P15">
-        <v>3.662755174000001</v>
+        <v>3.648905572000001</v>
       </c>
       <c r="Q15">
-        <v>5.722755174000001</v>
+        <v>5.708905572000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1116387463164237</v>
+        <v>0.1122534695177348</v>
       </c>
       <c r="T15">
-        <v>0.8580995758285324</v>
+        <v>0.8661114798791025</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.34357362760317</v>
+        <v>19.81903265420294</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1020307437852519</v>
+        <v>0.1018353582752152</v>
       </c>
       <c r="C16">
-        <v>33.4250814392751</v>
+        <v>33.19682987525908</v>
       </c>
       <c r="D16">
-        <v>35.77708143927509</v>
+        <v>35.90182987525909</v>
       </c>
       <c r="E16">
-        <v>-19.258</v>
+        <v>-18.905</v>
       </c>
       <c r="F16">
-        <v>4.942</v>
+        <v>5.295</v>
       </c>
       <c r="G16">
         <v>2.59</v>
@@ -2587,28 +2587,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M16">
-        <v>0.2485826</v>
+        <v>0.2663385</v>
       </c>
       <c r="N16">
-        <v>4.678084066666668</v>
+        <v>4.660328166666668</v>
       </c>
       <c r="O16">
-        <v>1.029178494666667</v>
+        <v>1.025272196666667</v>
       </c>
       <c r="P16">
-        <v>3.648905572000001</v>
+        <v>3.635055970000001</v>
       </c>
       <c r="Q16">
-        <v>5.708905572000001</v>
+        <v>5.69505597</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1122534695177348</v>
+        <v>0.1128826567943708</v>
       </c>
       <c r="T16">
-        <v>0.8661114798791025</v>
+        <v>0.8743118993190979</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.81903265420294</v>
+        <v>18.49776381058941</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1018353582752152</v>
+        <v>0.1016399727651785</v>
       </c>
       <c r="C17">
-        <v>33.19682987525908</v>
+        <v>32.96945130725597</v>
       </c>
       <c r="D17">
-        <v>35.90182987525909</v>
+        <v>36.02745130725597</v>
       </c>
       <c r="E17">
-        <v>-18.905</v>
+        <v>-18.552</v>
       </c>
       <c r="F17">
-        <v>5.294999999999999</v>
+        <v>5.648</v>
       </c>
       <c r="G17">
         <v>2.59</v>
@@ -2669,28 +2669,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M17">
-        <v>0.2663384999999999</v>
+        <v>0.2840944</v>
       </c>
       <c r="N17">
-        <v>4.660328166666668</v>
+        <v>4.642572266666668</v>
       </c>
       <c r="O17">
-        <v>1.025272196666667</v>
+        <v>1.021365898666667</v>
       </c>
       <c r="P17">
-        <v>3.635055970000001</v>
+        <v>3.621206368000001</v>
       </c>
       <c r="Q17">
-        <v>5.69505597</v>
+        <v>5.681206368000002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1128826567943708</v>
+        <v>0.1135268247204506</v>
       </c>
       <c r="T17">
-        <v>0.8743118993190979</v>
+        <v>0.8827075668409979</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.49776381058942</v>
+        <v>17.34165357242757</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1016399727651785</v>
+        <v>0.1014445872551418</v>
       </c>
       <c r="C18">
-        <v>32.96945130725597</v>
+        <v>32.74295493134996</v>
       </c>
       <c r="D18">
-        <v>36.02745130725597</v>
+        <v>36.15395493134996</v>
       </c>
       <c r="E18">
-        <v>-18.552</v>
+        <v>-18.199</v>
       </c>
       <c r="F18">
-        <v>5.648</v>
+        <v>6.001</v>
       </c>
       <c r="G18">
         <v>2.59</v>
@@ -2751,28 +2751,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M18">
-        <v>0.2840944</v>
+        <v>0.3018503</v>
       </c>
       <c r="N18">
-        <v>4.642572266666668</v>
+        <v>4.624816366666668</v>
       </c>
       <c r="O18">
-        <v>1.021365898666667</v>
+        <v>1.017459600666667</v>
       </c>
       <c r="P18">
-        <v>3.621206368000001</v>
+        <v>3.607356766000001</v>
       </c>
       <c r="Q18">
-        <v>5.681206368000002</v>
+        <v>5.667356766000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1135268247204506</v>
+        <v>0.1141865147652311</v>
       </c>
       <c r="T18">
-        <v>0.8827075668409979</v>
+        <v>0.8913055396043896</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.34165357242757</v>
+        <v>16.32155630346124</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1014445872551418</v>
+        <v>0.1012492017451052</v>
       </c>
       <c r="C19">
-        <v>32.74295493134996</v>
+        <v>32.51735007324176</v>
       </c>
       <c r="D19">
-        <v>36.15395493134996</v>
+        <v>36.28135007324175</v>
       </c>
       <c r="E19">
-        <v>-18.199</v>
+        <v>-17.846</v>
       </c>
       <c r="F19">
-        <v>6.001</v>
+        <v>6.354</v>
       </c>
       <c r="G19">
         <v>2.59</v>
@@ -2833,28 +2833,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M19">
-        <v>0.3018503</v>
+        <v>0.3196062</v>
       </c>
       <c r="N19">
-        <v>4.624816366666668</v>
+        <v>4.607060466666668</v>
       </c>
       <c r="O19">
-        <v>1.017459600666667</v>
+        <v>1.013553302666667</v>
       </c>
       <c r="P19">
-        <v>3.607356766000001</v>
+        <v>3.593507164000001</v>
       </c>
       <c r="Q19">
-        <v>5.667356766000001</v>
+        <v>5.653507164000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1141865147652311</v>
+        <v>0.1148622948111039</v>
       </c>
       <c r="T19">
-        <v>0.8913055396043896</v>
+        <v>0.900113219020547</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.32155630346124</v>
+        <v>15.41480317549117</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1012492017451052</v>
+        <v>0.1010538162350685</v>
       </c>
       <c r="C20">
-        <v>32.51735007324176</v>
+        <v>32.2926461905402</v>
       </c>
       <c r="D20">
-        <v>36.28135007324176</v>
+        <v>36.4096461905402</v>
       </c>
       <c r="E20">
-        <v>-17.846</v>
+        <v>-17.493</v>
       </c>
       <c r="F20">
-        <v>6.353999999999999</v>
+        <v>6.707</v>
       </c>
       <c r="G20">
         <v>2.59</v>
@@ -2915,28 +2915,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M20">
-        <v>0.3196062</v>
+        <v>0.3373621</v>
       </c>
       <c r="N20">
-        <v>4.607060466666668</v>
+        <v>4.589304566666668</v>
       </c>
       <c r="O20">
-        <v>1.013553302666667</v>
+        <v>1.009647004666667</v>
       </c>
       <c r="P20">
-        <v>3.593507164000001</v>
+        <v>3.579657562000001</v>
       </c>
       <c r="Q20">
-        <v>5.653507164000001</v>
+        <v>5.639657562000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1148622948111039</v>
+        <v>0.1155547607840351</v>
       </c>
       <c r="T20">
-        <v>0.9001132190205468</v>
+        <v>0.9091383720025351</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.41480317549118</v>
+        <v>14.60349774520217</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1010538162350685</v>
+        <v>0.1008584307250318</v>
       </c>
       <c r="C21">
-        <v>32.2926461905402</v>
+        <v>32.06885287510265</v>
       </c>
       <c r="D21">
-        <v>36.4096461905402</v>
+        <v>36.53885287510266</v>
       </c>
       <c r="E21">
-        <v>-17.493</v>
+        <v>-17.14</v>
       </c>
       <c r="F21">
-        <v>6.707</v>
+        <v>7.06</v>
       </c>
       <c r="G21">
         <v>2.59</v>
@@ -2997,28 +2997,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M21">
-        <v>0.3373621</v>
+        <v>0.355118</v>
       </c>
       <c r="N21">
-        <v>4.589304566666668</v>
+        <v>4.571548666666668</v>
       </c>
       <c r="O21">
-        <v>1.009647004666667</v>
+        <v>1.005740706666667</v>
       </c>
       <c r="P21">
-        <v>3.579657562000001</v>
+        <v>3.565807960000001</v>
       </c>
       <c r="Q21">
-        <v>5.639657562000001</v>
+        <v>5.625807960000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1155547607840351</v>
+        <v>0.1162645384062898</v>
       </c>
       <c r="T21">
-        <v>0.9091383720025351</v>
+        <v>0.9183891538090732</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.60349774520217</v>
+        <v>13.87332285794206</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1008584307250318</v>
+        <v>0.1006630452149951</v>
       </c>
       <c r="C22">
-        <v>32.06885287510265</v>
+        <v>31.84597985542575</v>
       </c>
       <c r="D22">
-        <v>36.53885287510266</v>
+        <v>36.66897985542575</v>
       </c>
       <c r="E22">
-        <v>-17.14</v>
+        <v>-16.787</v>
       </c>
       <c r="F22">
-        <v>7.06</v>
+        <v>7.413</v>
       </c>
       <c r="G22">
         <v>2.59</v>
@@ -3079,28 +3079,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M22">
-        <v>0.355118</v>
+        <v>0.3728739</v>
       </c>
       <c r="N22">
-        <v>4.571548666666668</v>
+        <v>4.553792766666668</v>
       </c>
       <c r="O22">
-        <v>1.005740706666667</v>
+        <v>1.001834408666667</v>
       </c>
       <c r="P22">
-        <v>3.565807960000001</v>
+        <v>3.551958358000001</v>
       </c>
       <c r="Q22">
-        <v>5.625807960000001</v>
+        <v>5.611958358000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1162645384062898</v>
+        <v>0.1169922850822723</v>
       </c>
       <c r="T22">
-        <v>0.9183891538090732</v>
+        <v>0.9278741326233717</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.87332285794206</v>
+        <v>13.21268843613529</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1006630452149951</v>
+        <v>0.1007250597049584</v>
       </c>
       <c r="C23">
-        <v>31.84597985542576</v>
+        <v>31.45157784156499</v>
       </c>
       <c r="D23">
-        <v>36.66897985542577</v>
+        <v>36.62757784156499</v>
       </c>
       <c r="E23">
-        <v>-16.787</v>
+        <v>-16.434</v>
       </c>
       <c r="F23">
-        <v>7.412999999999999</v>
+        <v>7.765999999999999</v>
       </c>
       <c r="G23">
         <v>2.59</v>
@@ -3161,45 +3161,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M23">
-        <v>0.3728738999999999</v>
+        <v>0.4022787999999999</v>
       </c>
       <c r="N23">
-        <v>4.553792766666668</v>
+        <v>4.524387866666668</v>
       </c>
       <c r="O23">
-        <v>1.001834408666667</v>
+        <v>0.995365330666667</v>
       </c>
       <c r="P23">
-        <v>3.551958358000001</v>
+        <v>3.529022536000001</v>
       </c>
       <c r="Q23">
-        <v>5.611958358000001</v>
+        <v>5.589022536000002</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1169922850822723</v>
+        <v>0.1177386919294339</v>
       </c>
       <c r="T23">
-        <v>0.9278741326233715</v>
+        <v>0.937602316022652</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.21268843613529</v>
+        <v>12.24689609958732</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1007250597049584</v>
+        <v>0.1005413741949217</v>
       </c>
       <c r="C24">
-        <v>31.45157784156499</v>
+        <v>31.22148223364837</v>
       </c>
       <c r="D24">
-        <v>36.62757784156499</v>
+        <v>36.75048223364837</v>
       </c>
       <c r="E24">
-        <v>-16.434</v>
+        <v>-16.081</v>
       </c>
       <c r="F24">
-        <v>7.765999999999999</v>
+        <v>8.119</v>
       </c>
       <c r="G24">
         <v>2.59</v>
@@ -3243,28 +3243,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M24">
-        <v>0.4022787999999999</v>
+        <v>0.4205642</v>
       </c>
       <c r="N24">
-        <v>4.524387866666668</v>
+        <v>4.506102466666667</v>
       </c>
       <c r="O24">
-        <v>0.995365330666667</v>
+        <v>0.9913425426666668</v>
       </c>
       <c r="P24">
-        <v>3.529022536000001</v>
+        <v>3.514759924000001</v>
       </c>
       <c r="Q24">
-        <v>5.589022536000002</v>
+        <v>5.574759924</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1177386919294339</v>
+        <v>0.1185044859674309</v>
       </c>
       <c r="T24">
-        <v>0.937602316022652</v>
+        <v>0.9475831795102256</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.24689609958732</v>
+        <v>11.714422356127</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1005413741949217</v>
+        <v>0.1003576886848851</v>
       </c>
       <c r="C25">
-        <v>31.22148223364837</v>
+        <v>30.99221421782701</v>
       </c>
       <c r="D25">
-        <v>36.75048223364837</v>
+        <v>36.87421421782701</v>
       </c>
       <c r="E25">
-        <v>-16.081</v>
+        <v>-15.728</v>
       </c>
       <c r="F25">
-        <v>8.119</v>
+        <v>8.472</v>
       </c>
       <c r="G25">
         <v>2.59</v>
@@ -3325,28 +3325,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M25">
-        <v>0.4205642</v>
+        <v>0.4388496</v>
       </c>
       <c r="N25">
-        <v>4.506102466666667</v>
+        <v>4.487817066666667</v>
       </c>
       <c r="O25">
-        <v>0.9913425426666668</v>
+        <v>0.9873197546666669</v>
       </c>
       <c r="P25">
-        <v>3.514759924000001</v>
+        <v>3.500497312000001</v>
       </c>
       <c r="Q25">
-        <v>5.574759924</v>
+        <v>5.560497312000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1185044859674309</v>
+        <v>0.1192904324801119</v>
       </c>
       <c r="T25">
-        <v>0.9475831795102256</v>
+        <v>0.9578266973001036</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.714422356127</v>
+        <v>11.22632142462171</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1003576886848851</v>
+        <v>0.1001740031748484</v>
       </c>
       <c r="C26">
-        <v>30.99221421782701</v>
+        <v>30.76378218138163</v>
       </c>
       <c r="D26">
-        <v>36.87421421782701</v>
+        <v>36.99878218138164</v>
       </c>
       <c r="E26">
-        <v>-15.728</v>
+        <v>-15.375</v>
       </c>
       <c r="F26">
-        <v>8.472</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="G26">
         <v>2.59</v>
@@ -3407,28 +3407,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M26">
-        <v>0.4388496</v>
+        <v>0.457135</v>
       </c>
       <c r="N26">
-        <v>4.487817066666667</v>
+        <v>4.469531666666668</v>
       </c>
       <c r="O26">
-        <v>0.9873197546666669</v>
+        <v>0.9832969666666669</v>
       </c>
       <c r="P26">
-        <v>3.500497312000001</v>
+        <v>3.486234700000001</v>
       </c>
       <c r="Q26">
-        <v>5.560497312000001</v>
+        <v>5.546234700000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1192904324801119</v>
+        <v>0.1200973375664645</v>
       </c>
       <c r="T26">
-        <v>0.9578266973001036</v>
+        <v>0.9683433755643783</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.22632142462171</v>
+        <v>10.77726856763684</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1001740031748484</v>
+        <v>0.09999031766481167</v>
       </c>
       <c r="C27">
-        <v>30.76378218138163</v>
+        <v>30.53619462531232</v>
       </c>
       <c r="D27">
-        <v>36.99878218138164</v>
+        <v>37.12419462531232</v>
       </c>
       <c r="E27">
-        <v>-15.375</v>
+        <v>-15.022</v>
       </c>
       <c r="F27">
-        <v>8.824999999999999</v>
+        <v>9.177999999999999</v>
       </c>
       <c r="G27">
         <v>2.59</v>
@@ -3489,28 +3489,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M27">
-        <v>0.457135</v>
+        <v>0.4754204</v>
       </c>
       <c r="N27">
-        <v>4.469531666666668</v>
+        <v>4.451246266666668</v>
       </c>
       <c r="O27">
-        <v>0.9832969666666669</v>
+        <v>0.9792741786666669</v>
       </c>
       <c r="P27">
-        <v>3.486234700000001</v>
+        <v>3.471972088000001</v>
       </c>
       <c r="Q27">
-        <v>5.546234700000001</v>
+        <v>5.531972088000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1200973375664645</v>
+        <v>0.1209260508983942</v>
       </c>
       <c r="T27">
-        <v>0.9683433755643783</v>
+        <v>0.9791442883763363</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.77726856763684</v>
+        <v>10.36275823811235</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09999031766481167</v>
+        <v>0.09980663215477502</v>
       </c>
       <c r="C28">
-        <v>30.53619462531232</v>
+        <v>30.30946016627232</v>
       </c>
       <c r="D28">
-        <v>37.12419462531232</v>
+        <v>37.25046016627233</v>
       </c>
       <c r="E28">
-        <v>-15.022</v>
+        <v>-14.669</v>
       </c>
       <c r="F28">
-        <v>9.177999999999999</v>
+        <v>9.531000000000001</v>
       </c>
       <c r="G28">
         <v>2.59</v>
@@ -3571,28 +3571,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M28">
-        <v>0.4754204</v>
+        <v>0.4937058</v>
       </c>
       <c r="N28">
-        <v>4.451246266666668</v>
+        <v>4.432960866666668</v>
       </c>
       <c r="O28">
-        <v>0.9792741786666669</v>
+        <v>0.9752513906666669</v>
       </c>
       <c r="P28">
-        <v>3.471972088000001</v>
+        <v>3.457709476000001</v>
       </c>
       <c r="Q28">
-        <v>5.531972088000001</v>
+        <v>5.517709476</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1209260508983942</v>
+        <v>0.1217774687051713</v>
       </c>
       <c r="T28">
-        <v>0.9791442883763363</v>
+        <v>0.9902411166077998</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.36275823811235</v>
+        <v>9.978952377441519</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09980663215477502</v>
+        <v>0.09999422664473832</v>
       </c>
       <c r="C29">
-        <v>30.30946016627232</v>
+        <v>29.82751689115929</v>
       </c>
       <c r="D29">
-        <v>37.25046016627233</v>
+        <v>37.1215168911593</v>
       </c>
       <c r="E29">
-        <v>-14.669</v>
+        <v>-14.316</v>
       </c>
       <c r="F29">
-        <v>9.531000000000001</v>
+        <v>9.884</v>
       </c>
       <c r="G29">
         <v>2.59</v>
@@ -3653,45 +3653,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M29">
-        <v>0.4937058</v>
+        <v>0.528794</v>
       </c>
       <c r="N29">
-        <v>4.432960866666668</v>
+        <v>4.397872666666668</v>
       </c>
       <c r="O29">
-        <v>0.9752513906666669</v>
+        <v>0.967531986666667</v>
       </c>
       <c r="P29">
-        <v>3.457709476000001</v>
+        <v>3.430340680000001</v>
       </c>
       <c r="Q29">
-        <v>5.517709476</v>
+        <v>5.490340680000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1217774687051713</v>
+        <v>0.122652537006581</v>
       </c>
       <c r="T29">
-        <v>0.9902411166077998</v>
+        <v>1.001646190067915</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.978952377441519</v>
+        <v>9.316797593517832</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09999422664473832</v>
+        <v>0.09982380113470166</v>
       </c>
       <c r="C30">
-        <v>29.82751689115929</v>
+        <v>29.59162182114628</v>
       </c>
       <c r="D30">
-        <v>37.1215168911593</v>
+        <v>37.23862182114629</v>
       </c>
       <c r="E30">
-        <v>-14.316</v>
+        <v>-13.963</v>
       </c>
       <c r="F30">
-        <v>9.884</v>
+        <v>10.237</v>
       </c>
       <c r="G30">
         <v>2.59</v>
@@ -3735,28 +3735,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M30">
-        <v>0.528794</v>
+        <v>0.5476795</v>
       </c>
       <c r="N30">
-        <v>4.397872666666668</v>
+        <v>4.378987166666668</v>
       </c>
       <c r="O30">
-        <v>0.967531986666667</v>
+        <v>0.9633771766666669</v>
       </c>
       <c r="P30">
-        <v>3.430340680000001</v>
+        <v>3.415609990000001</v>
       </c>
       <c r="Q30">
-        <v>5.490340680000001</v>
+        <v>5.475609990000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.122652537006581</v>
+        <v>0.1235522551192981</v>
       </c>
       <c r="T30">
-        <v>1.001646190067915</v>
+        <v>1.013372533202963</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.316797593517832</v>
+        <v>8.995528710982732</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09982380113470166</v>
+        <v>0.09965337562466496</v>
       </c>
       <c r="C31">
-        <v>29.59162182114629</v>
+        <v>29.35646793651637</v>
       </c>
       <c r="D31">
-        <v>37.23862182114629</v>
+        <v>37.35646793651637</v>
       </c>
       <c r="E31">
-        <v>-13.963</v>
+        <v>-13.61</v>
       </c>
       <c r="F31">
-        <v>10.237</v>
+        <v>10.59</v>
       </c>
       <c r="G31">
         <v>2.59</v>
@@ -3817,28 +3817,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M31">
-        <v>0.5476794999999999</v>
+        <v>0.5665649999999999</v>
       </c>
       <c r="N31">
-        <v>4.378987166666668</v>
+        <v>4.360101666666668</v>
       </c>
       <c r="O31">
-        <v>0.9633771766666669</v>
+        <v>0.9592223666666669</v>
       </c>
       <c r="P31">
-        <v>3.415609990000001</v>
+        <v>3.400879300000001</v>
       </c>
       <c r="Q31">
-        <v>5.475609990000001</v>
+        <v>5.460879300000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1235522551192981</v>
+        <v>0.1244776794638071</v>
       </c>
       <c r="T31">
-        <v>1.013372533202963</v>
+        <v>1.025433914713299</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.995528710982734</v>
+        <v>8.695677753949976</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09965337562466496</v>
+        <v>0.09948295011462825</v>
       </c>
       <c r="C32">
-        <v>29.35646793651637</v>
+        <v>29.12206229632068</v>
       </c>
       <c r="D32">
-        <v>37.35646793651637</v>
+        <v>37.47506229632067</v>
       </c>
       <c r="E32">
-        <v>-13.61</v>
+        <v>-13.257</v>
       </c>
       <c r="F32">
-        <v>10.59</v>
+        <v>10.943</v>
       </c>
       <c r="G32">
         <v>2.59</v>
@@ -3899,28 +3899,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M32">
-        <v>0.5665649999999999</v>
+        <v>0.5854505</v>
       </c>
       <c r="N32">
-        <v>4.360101666666668</v>
+        <v>4.341216166666667</v>
       </c>
       <c r="O32">
-        <v>0.9592223666666669</v>
+        <v>0.9550675566666668</v>
       </c>
       <c r="P32">
-        <v>3.400879300000001</v>
+        <v>3.386148610000001</v>
       </c>
       <c r="Q32">
-        <v>5.460879300000001</v>
+        <v>5.446148610000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1244776794638071</v>
+        <v>0.1254299277023598</v>
       </c>
       <c r="T32">
-        <v>1.025433914713299</v>
+        <v>1.037844901484803</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.695677753949976</v>
+        <v>8.415172019951587</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09948295011462825</v>
+        <v>0.0993125246045916</v>
       </c>
       <c r="C33">
-        <v>29.12206229632068</v>
+        <v>28.88841204953635</v>
       </c>
       <c r="D33">
-        <v>37.47506229632067</v>
+        <v>37.59441204953635</v>
       </c>
       <c r="E33">
-        <v>-13.257</v>
+        <v>-12.904</v>
       </c>
       <c r="F33">
-        <v>10.943</v>
+        <v>11.296</v>
       </c>
       <c r="G33">
         <v>2.59</v>
@@ -3981,28 +3981,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M33">
-        <v>0.5854505</v>
+        <v>0.604336</v>
       </c>
       <c r="N33">
-        <v>4.341216166666667</v>
+        <v>4.322330666666668</v>
       </c>
       <c r="O33">
-        <v>0.9550675566666668</v>
+        <v>0.9509127466666669</v>
       </c>
       <c r="P33">
-        <v>3.386148610000001</v>
+        <v>3.371417920000001</v>
       </c>
       <c r="Q33">
-        <v>5.446148610000001</v>
+        <v>5.431417920000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1254299277023598</v>
+        <v>0.1264101832420465</v>
       </c>
       <c r="T33">
-        <v>1.037844901484803</v>
+        <v>1.050620917278999</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.415172019951587</v>
+        <v>8.152197894328101</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0993125246045916</v>
+        <v>0.09914209909455489</v>
       </c>
       <c r="C34">
-        <v>28.88841204953635</v>
+        <v>28.65552443650326</v>
       </c>
       <c r="D34">
-        <v>37.59441204953635</v>
+        <v>37.71452443650326</v>
       </c>
       <c r="E34">
-        <v>-12.904</v>
+        <v>-12.551</v>
       </c>
       <c r="F34">
-        <v>11.296</v>
+        <v>11.649</v>
       </c>
       <c r="G34">
         <v>2.59</v>
@@ -4063,28 +4063,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M34">
-        <v>0.604336</v>
+        <v>0.6232215</v>
       </c>
       <c r="N34">
-        <v>4.322330666666668</v>
+        <v>4.303445166666668</v>
       </c>
       <c r="O34">
-        <v>0.9509127466666669</v>
+        <v>0.946757936666667</v>
       </c>
       <c r="P34">
-        <v>3.371417920000001</v>
+        <v>3.356687230000001</v>
       </c>
       <c r="Q34">
-        <v>5.431417920000001</v>
+        <v>5.416687230000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1264101832420465</v>
+        <v>0.1274197001411267</v>
       </c>
       <c r="T34">
-        <v>1.050620917278999</v>
+        <v>1.063778306678991</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.152197894328101</v>
+        <v>7.905161594499978</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09914209909455489</v>
+        <v>0.09897167358451821</v>
       </c>
       <c r="C35">
-        <v>28.65552443650326</v>
+        <v>28.42340679038789</v>
       </c>
       <c r="D35">
-        <v>37.71452443650326</v>
+        <v>37.83540679038789</v>
       </c>
       <c r="E35">
-        <v>-12.551</v>
+        <v>-12.198</v>
       </c>
       <c r="F35">
-        <v>11.649</v>
+        <v>12.002</v>
       </c>
       <c r="G35">
         <v>2.59</v>
@@ -4145,28 +4145,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M35">
-        <v>0.6232215</v>
+        <v>0.642107</v>
       </c>
       <c r="N35">
-        <v>4.303445166666668</v>
+        <v>4.284559666666667</v>
       </c>
       <c r="O35">
-        <v>0.946757936666667</v>
+        <v>0.9426031266666668</v>
       </c>
       <c r="P35">
-        <v>3.356687230000001</v>
+        <v>3.341956540000001</v>
       </c>
       <c r="Q35">
-        <v>5.416687230000001</v>
+        <v>5.40195654</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1274197001411267</v>
+        <v>0.1284598084613912</v>
       </c>
       <c r="T35">
-        <v>1.063778306678991</v>
+        <v>1.077334404848681</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.905161594499978</v>
+        <v>7.672656841720566</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09897167358451821</v>
+        <v>0.09901964807448152</v>
       </c>
       <c r="C36">
-        <v>28.42340679038789</v>
+        <v>28.03630032014624</v>
       </c>
       <c r="D36">
-        <v>37.83540679038789</v>
+        <v>37.80130032014625</v>
       </c>
       <c r="E36">
-        <v>-12.198</v>
+        <v>-11.845</v>
       </c>
       <c r="F36">
-        <v>12.002</v>
+        <v>12.355</v>
       </c>
       <c r="G36">
         <v>2.59</v>
@@ -4227,45 +4227,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M36">
-        <v>0.642107</v>
+        <v>0.6708765</v>
       </c>
       <c r="N36">
-        <v>4.284559666666667</v>
+        <v>4.255790166666667</v>
       </c>
       <c r="O36">
-        <v>0.9426031266666668</v>
+        <v>0.9362738366666669</v>
       </c>
       <c r="P36">
-        <v>3.341956540000001</v>
+        <v>3.31951633</v>
       </c>
       <c r="Q36">
-        <v>5.40195654</v>
+        <v>5.37951633</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1284598084613912</v>
+        <v>0.129531920114587</v>
       </c>
       <c r="T36">
-        <v>1.077334404848681</v>
+        <v>1.091307613731284</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.672656841720566</v>
+        <v>7.343626832459726</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09901964807448152</v>
+        <v>0.09885546256444486</v>
       </c>
       <c r="C37">
-        <v>28.03630032014624</v>
+        <v>27.80028027797007</v>
       </c>
       <c r="D37">
-        <v>37.80130032014625</v>
+        <v>37.91828027797007</v>
       </c>
       <c r="E37">
-        <v>-11.845</v>
+        <v>-11.492</v>
       </c>
       <c r="F37">
-        <v>12.355</v>
+        <v>12.708</v>
       </c>
       <c r="G37">
         <v>2.59</v>
@@ -4309,28 +4309,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M37">
-        <v>0.6708765</v>
+        <v>0.6900444</v>
       </c>
       <c r="N37">
-        <v>4.255790166666667</v>
+        <v>4.236622266666668</v>
       </c>
       <c r="O37">
-        <v>0.9362738366666669</v>
+        <v>0.932056898666667</v>
       </c>
       <c r="P37">
-        <v>3.31951633</v>
+        <v>3.304565368000001</v>
       </c>
       <c r="Q37">
-        <v>5.37951633</v>
+        <v>5.364565368000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.129531920114587</v>
+        <v>0.1306375352569451</v>
       </c>
       <c r="T37">
-        <v>1.091307613731284</v>
+        <v>1.105717485391468</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.343626832459726</v>
+        <v>7.139637198224735</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09885546256444486</v>
+        <v>0.09869127705440817</v>
       </c>
       <c r="C38">
-        <v>27.80028027797007</v>
+        <v>27.56498649596795</v>
       </c>
       <c r="D38">
-        <v>37.91828027797007</v>
+        <v>38.03598649596795</v>
       </c>
       <c r="E38">
-        <v>-11.492</v>
+        <v>-11.139</v>
       </c>
       <c r="F38">
-        <v>12.708</v>
+        <v>13.061</v>
       </c>
       <c r="G38">
         <v>2.59</v>
@@ -4391,28 +4391,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M38">
-        <v>0.6900443999999999</v>
+        <v>0.7092122999999999</v>
       </c>
       <c r="N38">
-        <v>4.236622266666668</v>
+        <v>4.217454366666668</v>
       </c>
       <c r="O38">
-        <v>0.932056898666667</v>
+        <v>0.9278399606666669</v>
       </c>
       <c r="P38">
-        <v>3.304565368000001</v>
+        <v>3.289614406000001</v>
       </c>
       <c r="Q38">
-        <v>5.364565368000001</v>
+        <v>5.349614406000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1306375352569451</v>
+        <v>0.1317782492927114</v>
       </c>
       <c r="T38">
-        <v>1.105717485391468</v>
+        <v>1.120584813294832</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.139637198224736</v>
+        <v>6.946674030705148</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09869127705440817</v>
+        <v>0.09852709154437148</v>
       </c>
       <c r="C39">
-        <v>27.56498649596795</v>
+        <v>27.33042575858751</v>
       </c>
       <c r="D39">
-        <v>38.03598649596795</v>
+        <v>38.15442575858751</v>
       </c>
       <c r="E39">
-        <v>-11.139</v>
+        <v>-10.786</v>
       </c>
       <c r="F39">
-        <v>13.061</v>
+        <v>13.414</v>
       </c>
       <c r="G39">
         <v>2.59</v>
@@ -4473,28 +4473,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M39">
-        <v>0.7092122999999999</v>
+        <v>0.7283802</v>
       </c>
       <c r="N39">
-        <v>4.217454366666668</v>
+        <v>4.198286466666667</v>
       </c>
       <c r="O39">
-        <v>0.9278399606666669</v>
+        <v>0.9236230226666668</v>
       </c>
       <c r="P39">
-        <v>3.289614406000001</v>
+        <v>3.274663444000001</v>
       </c>
       <c r="Q39">
-        <v>5.349614406000001</v>
+        <v>5.334663444</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1317782492927114</v>
+        <v>0.1329557605554379</v>
       </c>
       <c r="T39">
-        <v>1.120584813294832</v>
+        <v>1.135931732420886</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.946674030705148</v>
+        <v>6.7638668193708</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09852709154437148</v>
+        <v>0.0983629060343348</v>
       </c>
       <c r="C40">
-        <v>27.33042575858751</v>
+        <v>27.09660493504397</v>
       </c>
       <c r="D40">
-        <v>38.15442575858751</v>
+        <v>38.27360493504397</v>
       </c>
       <c r="E40">
-        <v>-10.786</v>
+        <v>-10.433</v>
       </c>
       <c r="F40">
-        <v>13.414</v>
+        <v>13.767</v>
       </c>
       <c r="G40">
         <v>2.59</v>
@@ -4555,28 +4555,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M40">
-        <v>0.7283802</v>
+        <v>0.7475480999999999</v>
       </c>
       <c r="N40">
-        <v>4.198286466666667</v>
+        <v>4.179118566666668</v>
       </c>
       <c r="O40">
-        <v>0.9236230226666668</v>
+        <v>0.919406084666667</v>
       </c>
       <c r="P40">
-        <v>3.274663444000001</v>
+        <v>3.259712482000001</v>
       </c>
       <c r="Q40">
-        <v>5.334663444</v>
+        <v>5.319712482000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1329557605554379</v>
+        <v>0.1341718787448112</v>
       </c>
       <c r="T40">
-        <v>1.135931732420886</v>
+        <v>1.151781829223204</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.7638668193708</v>
+        <v>6.590434336822833</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0983629060343348</v>
+        <v>0.09819872052429811</v>
       </c>
       <c r="C41">
-        <v>27.09660493504397</v>
+        <v>26.86353098064826</v>
       </c>
       <c r="D41">
-        <v>38.27360493504397</v>
+        <v>38.39353098064825</v>
       </c>
       <c r="E41">
-        <v>-10.433</v>
+        <v>-10.08</v>
       </c>
       <c r="F41">
-        <v>13.767</v>
+        <v>14.12</v>
       </c>
       <c r="G41">
         <v>2.59</v>
@@ -4637,28 +4637,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M41">
-        <v>0.7475480999999999</v>
+        <v>0.766716</v>
       </c>
       <c r="N41">
-        <v>4.179118566666668</v>
+        <v>4.159950666666668</v>
       </c>
       <c r="O41">
-        <v>0.919406084666667</v>
+        <v>0.915189146666667</v>
       </c>
       <c r="P41">
-        <v>3.259712482000001</v>
+        <v>3.244761520000001</v>
       </c>
       <c r="Q41">
-        <v>5.319712482000002</v>
+        <v>5.304761520000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1341718787448112</v>
+        <v>0.1354285342071635</v>
       </c>
       <c r="T41">
-        <v>1.151781829223204</v>
+        <v>1.168160262585599</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.590434336822833</v>
+        <v>6.425673478402262</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09819872052429811</v>
+        <v>0.09803453501426143</v>
       </c>
       <c r="C42">
-        <v>26.86353098064826</v>
+        <v>26.63121093816</v>
       </c>
       <c r="D42">
-        <v>38.39353098064825</v>
+        <v>38.51421093815999</v>
       </c>
       <c r="E42">
-        <v>-10.08</v>
+        <v>-9.726999999999999</v>
       </c>
       <c r="F42">
-        <v>14.12</v>
+        <v>14.473</v>
       </c>
       <c r="G42">
         <v>2.59</v>
@@ -4719,28 +4719,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M42">
-        <v>0.766716</v>
+        <v>0.7858839000000001</v>
       </c>
       <c r="N42">
-        <v>4.159950666666668</v>
+        <v>4.140782766666668</v>
       </c>
       <c r="O42">
-        <v>0.915189146666667</v>
+        <v>0.9109722086666668</v>
       </c>
       <c r="P42">
-        <v>3.244761520000001</v>
+        <v>3.229810558000001</v>
       </c>
       <c r="Q42">
-        <v>5.304761520000001</v>
+        <v>5.289810558000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1354285342071635</v>
+        <v>0.1367277881597651</v>
       </c>
       <c r="T42">
-        <v>1.168160262585599</v>
+        <v>1.185093897078923</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.425673478402262</v>
+        <v>6.268949735026595</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09803453501426143</v>
+        <v>0.09787034950422474</v>
       </c>
       <c r="C43">
-        <v>26.63121093816</v>
+        <v>26.39965193916633</v>
       </c>
       <c r="D43">
-        <v>38.51421093815999</v>
+        <v>38.63565193916633</v>
       </c>
       <c r="E43">
-        <v>-9.726999999999999</v>
+        <v>-9.373999999999999</v>
       </c>
       <c r="F43">
-        <v>14.473</v>
+        <v>14.826</v>
       </c>
       <c r="G43">
         <v>2.59</v>
@@ -4801,28 +4801,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M43">
-        <v>0.7858839000000001</v>
+        <v>0.8050518000000001</v>
       </c>
       <c r="N43">
-        <v>4.140782766666668</v>
+        <v>4.121614866666667</v>
       </c>
       <c r="O43">
-        <v>0.9109722086666668</v>
+        <v>0.9067552706666668</v>
       </c>
       <c r="P43">
-        <v>3.229810558000001</v>
+        <v>3.214859596000001</v>
       </c>
       <c r="Q43">
-        <v>5.289810558000001</v>
+        <v>5.274859596000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1367277881597651</v>
+        <v>0.1380718439728013</v>
       </c>
       <c r="T43">
-        <v>1.185093897078923</v>
+        <v>1.202611450003051</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.268949735026595</v>
+        <v>6.119689027049771</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09787034950422475</v>
+        <v>0.09804156399418806</v>
       </c>
       <c r="C44">
-        <v>26.39965193916631</v>
+        <v>25.9200289413958</v>
       </c>
       <c r="D44">
-        <v>38.63565193916632</v>
+        <v>38.5090289413958</v>
       </c>
       <c r="E44">
-        <v>-9.374000000000001</v>
+        <v>-9.021000000000001</v>
       </c>
       <c r="F44">
-        <v>14.826</v>
+        <v>15.179</v>
       </c>
       <c r="G44">
         <v>2.59</v>
@@ -4883,45 +4883,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M44">
-        <v>0.8050518</v>
+        <v>0.8393986999999999</v>
       </c>
       <c r="N44">
-        <v>4.121614866666667</v>
+        <v>4.087267966666667</v>
       </c>
       <c r="O44">
-        <v>0.9067552706666668</v>
+        <v>0.8991989526666668</v>
       </c>
       <c r="P44">
-        <v>3.214859596000001</v>
+        <v>3.188069014000001</v>
       </c>
       <c r="Q44">
-        <v>5.274859596000001</v>
+        <v>5.248069014</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1380718439728013</v>
+        <v>0.1394630596389264</v>
       </c>
       <c r="T44">
-        <v>1.202611450003051</v>
+        <v>1.220743653906973</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.119689027049771</v>
+        <v>5.86928079191291</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09804156399418806</v>
+        <v>0.0978851784841514</v>
       </c>
       <c r="C45">
-        <v>25.9200289413958</v>
+        <v>25.68265212456008</v>
       </c>
       <c r="D45">
-        <v>38.5090289413958</v>
+        <v>38.62465212456007</v>
       </c>
       <c r="E45">
-        <v>-9.021000000000001</v>
+        <v>-8.668000000000001</v>
       </c>
       <c r="F45">
-        <v>15.179</v>
+        <v>15.532</v>
       </c>
       <c r="G45">
         <v>2.59</v>
@@ -4965,28 +4965,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M45">
-        <v>0.8393986999999999</v>
+        <v>0.8589195999999999</v>
       </c>
       <c r="N45">
-        <v>4.087267966666667</v>
+        <v>4.067747066666668</v>
       </c>
       <c r="O45">
-        <v>0.8991989526666668</v>
+        <v>0.8949043546666668</v>
       </c>
       <c r="P45">
-        <v>3.188069014000001</v>
+        <v>3.172842712</v>
       </c>
       <c r="Q45">
-        <v>5.248069014</v>
+        <v>5.232842712</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1394630596389264</v>
+        <v>0.1409039615788418</v>
       </c>
       <c r="T45">
-        <v>1.220743653906973</v>
+        <v>1.23952343652175</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.86928079191291</v>
+        <v>5.735888046642163</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0978851784841514</v>
+        <v>0.09772879297411471</v>
       </c>
       <c r="C46">
-        <v>25.68265212456008</v>
+        <v>25.44597171484016</v>
       </c>
       <c r="D46">
-        <v>38.62465212456007</v>
+        <v>38.74097171484016</v>
       </c>
       <c r="E46">
-        <v>-8.668000000000001</v>
+        <v>-8.315</v>
       </c>
       <c r="F46">
-        <v>15.532</v>
+        <v>15.885</v>
       </c>
       <c r="G46">
         <v>2.59</v>
@@ -5047,28 +5047,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M46">
-        <v>0.8589195999999999</v>
+        <v>0.8784405000000001</v>
       </c>
       <c r="N46">
-        <v>4.067747066666668</v>
+        <v>4.048226166666668</v>
       </c>
       <c r="O46">
-        <v>0.8949043546666668</v>
+        <v>0.8906097566666669</v>
       </c>
       <c r="P46">
-        <v>3.172842712</v>
+        <v>3.157616410000001</v>
       </c>
       <c r="Q46">
-        <v>5.232842712</v>
+        <v>5.217616410000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1409039615788418</v>
+        <v>0.1423972599529358</v>
       </c>
       <c r="T46">
-        <v>1.23952343652175</v>
+        <v>1.258986120322518</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.735888046642163</v>
+        <v>5.608423867827892</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09772879297411471</v>
+        <v>0.09757240746407801</v>
       </c>
       <c r="C47">
-        <v>25.44597171484016</v>
+        <v>25.20999402300976</v>
       </c>
       <c r="D47">
-        <v>38.74097171484016</v>
+        <v>38.85799402300975</v>
       </c>
       <c r="E47">
-        <v>-8.315</v>
+        <v>-7.962</v>
       </c>
       <c r="F47">
-        <v>15.885</v>
+        <v>16.238</v>
       </c>
       <c r="G47">
         <v>2.59</v>
@@ -5129,28 +5129,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M47">
-        <v>0.8784405000000001</v>
+        <v>0.8979614</v>
       </c>
       <c r="N47">
-        <v>4.048226166666668</v>
+        <v>4.028705266666668</v>
       </c>
       <c r="O47">
-        <v>0.8906097566666669</v>
+        <v>0.8863151586666669</v>
       </c>
       <c r="P47">
-        <v>3.157616410000001</v>
+        <v>3.142390108000001</v>
       </c>
       <c r="Q47">
-        <v>5.217616410000002</v>
+        <v>5.202390108000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1423972599529358</v>
+        <v>0.1439458656742185</v>
       </c>
       <c r="T47">
-        <v>1.258986120322518</v>
+        <v>1.279169644264055</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.608423867827892</v>
+        <v>5.486501609831634</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09757240746407801</v>
+        <v>0.09741602195404134</v>
       </c>
       <c r="C48">
-        <v>25.20999402300976</v>
+        <v>24.97472543632365</v>
       </c>
       <c r="D48">
-        <v>38.85799402300975</v>
+        <v>38.97572543632365</v>
       </c>
       <c r="E48">
-        <v>-7.962</v>
+        <v>-7.608999999999998</v>
       </c>
       <c r="F48">
-        <v>16.238</v>
+        <v>16.591</v>
       </c>
       <c r="G48">
         <v>2.59</v>
@@ -5211,28 +5211,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M48">
-        <v>0.8979614</v>
+        <v>0.9174823000000001</v>
       </c>
       <c r="N48">
-        <v>4.028705266666668</v>
+        <v>4.009184366666668</v>
       </c>
       <c r="O48">
-        <v>0.8863151586666669</v>
+        <v>0.882020560666667</v>
       </c>
       <c r="P48">
-        <v>3.142390108000001</v>
+        <v>3.127163806000001</v>
       </c>
       <c r="Q48">
-        <v>5.202390108000001</v>
+        <v>5.187163806000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1439458656742185</v>
+        <v>0.1455529093472478</v>
       </c>
       <c r="T48">
-        <v>1.279169644264055</v>
+        <v>1.300114810618481</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.486501609831634</v>
+        <v>5.369767533026706</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09741602195404134</v>
+        <v>0.09725963644400465</v>
       </c>
       <c r="C49">
-        <v>24.97472543632365</v>
+        <v>24.74017241968005</v>
       </c>
       <c r="D49">
-        <v>38.97572543632365</v>
+        <v>39.09417241968005</v>
       </c>
       <c r="E49">
-        <v>-7.608999999999998</v>
+        <v>-7.256</v>
       </c>
       <c r="F49">
-        <v>16.591</v>
+        <v>16.944</v>
       </c>
       <c r="G49">
         <v>2.59</v>
@@ -5293,28 +5293,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M49">
-        <v>0.9174823000000001</v>
+        <v>0.9370032</v>
       </c>
       <c r="N49">
-        <v>4.009184366666668</v>
+        <v>3.989663466666668</v>
       </c>
       <c r="O49">
-        <v>0.882020560666667</v>
+        <v>0.8777259626666669</v>
       </c>
       <c r="P49">
-        <v>3.127163806000001</v>
+        <v>3.111937504000001</v>
       </c>
       <c r="Q49">
-        <v>5.187163806000001</v>
+        <v>5.171937504000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1455529093472478</v>
+        <v>0.1472217623923166</v>
       </c>
       <c r="T49">
-        <v>1.300114810618481</v>
+        <v>1.321865560294231</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.369767533026706</v>
+        <v>5.257897376088649</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09725963644400464</v>
+        <v>0.09710325093396796</v>
       </c>
       <c r="C50">
-        <v>24.74017241968007</v>
+        <v>24.5063415168038</v>
       </c>
       <c r="D50">
-        <v>39.09417241968006</v>
+        <v>39.21334151680379</v>
       </c>
       <c r="E50">
-        <v>-7.256</v>
+        <v>-6.903000000000002</v>
       </c>
       <c r="F50">
-        <v>16.944</v>
+        <v>17.297</v>
       </c>
       <c r="G50">
         <v>2.59</v>
@@ -5375,28 +5375,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M50">
-        <v>0.9370032</v>
+        <v>0.9565240999999999</v>
       </c>
       <c r="N50">
-        <v>3.989663466666668</v>
+        <v>3.970142566666668</v>
       </c>
       <c r="O50">
-        <v>0.8777259626666669</v>
+        <v>0.8734313646666669</v>
       </c>
       <c r="P50">
-        <v>3.111937504000001</v>
+        <v>3.096711202000001</v>
       </c>
       <c r="Q50">
-        <v>5.171937504000001</v>
+        <v>5.156711202</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1472217623923166</v>
+        <v>0.1489560606548391</v>
       </c>
       <c r="T50">
-        <v>1.321865560294231</v>
+        <v>1.3444692805455</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.257897376088649</v>
+        <v>5.150593348005208</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09710325093396796</v>
+        <v>0.09694686542393129</v>
       </c>
       <c r="C51">
-        <v>24.5063415168038</v>
+        <v>24.27323935145152</v>
       </c>
       <c r="D51">
-        <v>39.21334151680379</v>
+        <v>39.33323935145151</v>
       </c>
       <c r="E51">
-        <v>-6.903000000000002</v>
+        <v>-6.550000000000001</v>
       </c>
       <c r="F51">
-        <v>17.297</v>
+        <v>17.65</v>
       </c>
       <c r="G51">
         <v>2.59</v>
@@ -5457,28 +5457,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M51">
-        <v>0.9565240999999999</v>
+        <v>0.9760449999999999</v>
       </c>
       <c r="N51">
-        <v>3.970142566666668</v>
+        <v>3.950621666666668</v>
       </c>
       <c r="O51">
-        <v>0.8734313646666669</v>
+        <v>0.8691367666666668</v>
       </c>
       <c r="P51">
-        <v>3.096711202000001</v>
+        <v>3.081484900000001</v>
       </c>
       <c r="Q51">
-        <v>5.156711202</v>
+        <v>5.141484900000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1489560606548391</v>
+        <v>0.1507597308478626</v>
       </c>
       <c r="T51">
-        <v>1.3444692805455</v>
+        <v>1.36797714960682</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.150593348005208</v>
+        <v>5.047581481045103</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09694686542393129</v>
+        <v>0.0967904799138946</v>
       </c>
       <c r="C52">
-        <v>24.27323935145152</v>
+        <v>24.04087262863892</v>
       </c>
       <c r="D52">
-        <v>39.33323935145151</v>
+        <v>39.45387262863893</v>
       </c>
       <c r="E52">
-        <v>-6.550000000000001</v>
+        <v>-6.196999999999999</v>
       </c>
       <c r="F52">
-        <v>17.65</v>
+        <v>18.003</v>
       </c>
       <c r="G52">
         <v>2.59</v>
@@ -5539,28 +5539,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M52">
-        <v>0.9760449999999999</v>
+        <v>0.9955659</v>
       </c>
       <c r="N52">
-        <v>3.950621666666668</v>
+        <v>3.931100766666668</v>
       </c>
       <c r="O52">
-        <v>0.8691367666666668</v>
+        <v>0.8648421686666669</v>
       </c>
       <c r="P52">
-        <v>3.081484900000001</v>
+        <v>3.066258598000001</v>
       </c>
       <c r="Q52">
-        <v>5.141484900000001</v>
+        <v>5.126258598000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1507597308478626</v>
+        <v>0.1526370202324379</v>
       </c>
       <c r="T52">
-        <v>1.36797714960682</v>
+        <v>1.392444523527786</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.047581481045103</v>
+        <v>4.948609295142258</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0967904799138946</v>
+        <v>0.09663409440385792</v>
       </c>
       <c r="C53">
-        <v>24.04087262863892</v>
+        <v>23.80924813589068</v>
       </c>
       <c r="D53">
-        <v>39.45387262863893</v>
+        <v>39.57524813589067</v>
       </c>
       <c r="E53">
-        <v>-6.196999999999999</v>
+        <v>-5.844000000000001</v>
       </c>
       <c r="F53">
-        <v>18.003</v>
+        <v>18.356</v>
       </c>
       <c r="G53">
         <v>2.59</v>
@@ -5621,28 +5621,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M53">
-        <v>0.9955659</v>
+        <v>1.0150868</v>
       </c>
       <c r="N53">
-        <v>3.931100766666668</v>
+        <v>3.911579866666668</v>
       </c>
       <c r="O53">
-        <v>0.8648421686666669</v>
+        <v>0.860547570666667</v>
       </c>
       <c r="P53">
-        <v>3.066258598000001</v>
+        <v>3.051032296000001</v>
       </c>
       <c r="Q53">
-        <v>5.126258598000001</v>
+        <v>5.111032296000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1526370202324379</v>
+        <v>0.1545925300080373</v>
       </c>
       <c r="T53">
-        <v>1.392444523527786</v>
+        <v>1.417931371362126</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.948609295142258</v>
+        <v>4.853443731774139</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09663409440385792</v>
+        <v>0.09647770889382121</v>
       </c>
       <c r="C54">
-        <v>23.80924813589068</v>
+        <v>23.57837274451353</v>
       </c>
       <c r="D54">
-        <v>39.57524813589067</v>
+        <v>39.69737274451353</v>
       </c>
       <c r="E54">
-        <v>-5.844000000000001</v>
+        <v>-5.491</v>
       </c>
       <c r="F54">
-        <v>18.356</v>
+        <v>18.709</v>
       </c>
       <c r="G54">
         <v>2.59</v>
@@ -5703,28 +5703,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M54">
-        <v>1.0150868</v>
+        <v>1.0346077</v>
       </c>
       <c r="N54">
-        <v>3.911579866666668</v>
+        <v>3.892058966666668</v>
       </c>
       <c r="O54">
-        <v>0.860547570666667</v>
+        <v>0.8562529726666669</v>
       </c>
       <c r="P54">
-        <v>3.051032296000001</v>
+        <v>3.035805994000001</v>
       </c>
       <c r="Q54">
-        <v>5.111032296000001</v>
+        <v>5.095805994000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1545925300080373</v>
+        <v>0.1566312529655771</v>
       </c>
       <c r="T54">
-        <v>1.417931371362126</v>
+        <v>1.44450276591282</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.853443731774139</v>
+        <v>4.761869321740663</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09647770889382121</v>
+        <v>0.09632132338378455</v>
       </c>
       <c r="C55">
-        <v>23.57837274451353</v>
+        <v>23.34825341089288</v>
       </c>
       <c r="D55">
-        <v>39.69737274451353</v>
+        <v>39.82025341089287</v>
       </c>
       <c r="E55">
-        <v>-5.491</v>
+        <v>-5.137999999999998</v>
       </c>
       <c r="F55">
-        <v>18.709</v>
+        <v>19.062</v>
       </c>
       <c r="G55">
         <v>2.59</v>
@@ -5785,28 +5785,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M55">
-        <v>1.0346077</v>
+        <v>1.0541286</v>
       </c>
       <c r="N55">
-        <v>3.892058966666668</v>
+        <v>3.872538066666667</v>
       </c>
       <c r="O55">
-        <v>0.8562529726666669</v>
+        <v>0.8519583746666668</v>
       </c>
       <c r="P55">
-        <v>3.035805994000001</v>
+        <v>3.020579692000001</v>
       </c>
       <c r="Q55">
-        <v>5.095805994000001</v>
+        <v>5.080579692000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1566312529655771</v>
+        <v>0.1587586160517055</v>
       </c>
       <c r="T55">
-        <v>1.44450276591282</v>
+        <v>1.472229438487457</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.761869321740663</v>
+        <v>4.673686556523243</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09632132338378455</v>
+        <v>0.09616493787374784</v>
       </c>
       <c r="C56">
-        <v>23.34825341089288</v>
+        <v>23.1188971778139</v>
       </c>
       <c r="D56">
-        <v>39.82025341089287</v>
+        <v>39.9438971778139</v>
       </c>
       <c r="E56">
-        <v>-5.137999999999998</v>
+        <v>-4.785</v>
       </c>
       <c r="F56">
-        <v>19.062</v>
+        <v>19.415</v>
       </c>
       <c r="G56">
         <v>2.59</v>
@@ -5867,28 +5867,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M56">
-        <v>1.0541286</v>
+        <v>1.0736495</v>
       </c>
       <c r="N56">
-        <v>3.872538066666667</v>
+        <v>3.853017166666667</v>
       </c>
       <c r="O56">
-        <v>0.8519583746666668</v>
+        <v>0.8476637766666668</v>
       </c>
       <c r="P56">
-        <v>3.020579692000001</v>
+        <v>3.005353390000001</v>
       </c>
       <c r="Q56">
-        <v>5.080579692000001</v>
+        <v>5.06535339</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1587586160517055</v>
+        <v>0.1609805286083286</v>
       </c>
       <c r="T56">
-        <v>1.472229438487457</v>
+        <v>1.501188407620968</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.673686556523243</v>
+        <v>4.588710437313731</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09616493787374784</v>
+        <v>0.09600855236371117</v>
       </c>
       <c r="C57">
-        <v>23.1188971778139</v>
+        <v>22.89031117580679</v>
       </c>
       <c r="D57">
-        <v>39.9438971778139</v>
+        <v>40.06831117580679</v>
       </c>
       <c r="E57">
-        <v>-4.785</v>
+        <v>-4.431999999999999</v>
       </c>
       <c r="F57">
-        <v>19.415</v>
+        <v>19.768</v>
       </c>
       <c r="G57">
         <v>2.59</v>
@@ -5949,28 +5949,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M57">
-        <v>1.0736495</v>
+        <v>1.0931704</v>
       </c>
       <c r="N57">
-        <v>3.853017166666667</v>
+        <v>3.833496266666668</v>
       </c>
       <c r="O57">
-        <v>0.8476637766666668</v>
+        <v>0.8433691786666669</v>
       </c>
       <c r="P57">
-        <v>3.005353390000001</v>
+        <v>2.990127088000001</v>
       </c>
       <c r="Q57">
-        <v>5.06535339</v>
+        <v>5.050127088000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1609805286083286</v>
+        <v>0.1633034371902527</v>
       </c>
       <c r="T57">
-        <v>1.501188407620968</v>
+        <v>1.531463693533274</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.588710437313731</v>
+        <v>4.506769179504556</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09600855236371117</v>
+        <v>0.0969636668536745</v>
       </c>
       <c r="C58">
-        <v>22.89031117580679</v>
+        <v>21.78932286797455</v>
       </c>
       <c r="D58">
-        <v>40.06831117580679</v>
+        <v>39.32032286797455</v>
       </c>
       <c r="E58">
-        <v>-4.431999999999999</v>
+        <v>-4.078999999999997</v>
       </c>
       <c r="F58">
-        <v>19.768</v>
+        <v>20.121</v>
       </c>
       <c r="G58">
         <v>2.59</v>
@@ -6031,45 +6031,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M58">
-        <v>1.0931704</v>
+        <v>1.1629938</v>
       </c>
       <c r="N58">
-        <v>3.833496266666668</v>
+        <v>3.763672866666667</v>
       </c>
       <c r="O58">
-        <v>0.8433691786666669</v>
+        <v>0.8280080306666668</v>
       </c>
       <c r="P58">
-        <v>2.990127088000001</v>
+        <v>2.935664836000001</v>
       </c>
       <c r="Q58">
-        <v>5.050127088000001</v>
+        <v>4.995664836000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1633034371902527</v>
+        <v>0.1657343880318012</v>
       </c>
       <c r="T58">
-        <v>1.531463693533274</v>
+        <v>1.563147132278711</v>
       </c>
       <c r="U58">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.506769179504556</v>
+        <v>4.236193405903512</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0969636668536745</v>
+        <v>0.09682678134363781</v>
       </c>
       <c r="C59">
-        <v>21.78932286797455</v>
+        <v>21.54180438785217</v>
       </c>
       <c r="D59">
-        <v>39.32032286797455</v>
+        <v>39.42580438785217</v>
       </c>
       <c r="E59">
-        <v>-4.078999999999997</v>
+        <v>-3.725999999999999</v>
       </c>
       <c r="F59">
-        <v>20.121</v>
+        <v>20.474</v>
       </c>
       <c r="G59">
         <v>2.59</v>
@@ -6113,28 +6113,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M59">
-        <v>1.1629938</v>
+        <v>1.1833972</v>
       </c>
       <c r="N59">
-        <v>3.763672866666667</v>
+        <v>3.743269466666668</v>
       </c>
       <c r="O59">
-        <v>0.8280080306666668</v>
+        <v>0.8235192826666669</v>
       </c>
       <c r="P59">
-        <v>2.935664836000001</v>
+        <v>2.919750184000001</v>
       </c>
       <c r="Q59">
-        <v>4.995664836000001</v>
+        <v>4.979750184</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1657343880318012</v>
+        <v>0.1682810984372329</v>
       </c>
       <c r="T59">
-        <v>1.563147132278711</v>
+        <v>1.596339306202502</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.236193405903512</v>
+        <v>4.163155588560347</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0968267813436378</v>
+        <v>0.09668989583360113</v>
       </c>
       <c r="C60">
-        <v>21.54180438785219</v>
+        <v>21.29485336385881</v>
       </c>
       <c r="D60">
-        <v>39.42580438785218</v>
+        <v>39.5318533638588</v>
       </c>
       <c r="E60">
-        <v>-3.726000000000003</v>
+        <v>-3.373000000000001</v>
       </c>
       <c r="F60">
-        <v>20.474</v>
+        <v>20.827</v>
       </c>
       <c r="G60">
         <v>2.59</v>
@@ -6195,28 +6195,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M60">
-        <v>1.1833972</v>
+        <v>1.2038006</v>
       </c>
       <c r="N60">
-        <v>3.743269466666668</v>
+        <v>3.722866066666668</v>
       </c>
       <c r="O60">
-        <v>0.8235192826666669</v>
+        <v>0.8190305346666669</v>
       </c>
       <c r="P60">
-        <v>2.919750184000001</v>
+        <v>2.903835532</v>
       </c>
       <c r="Q60">
-        <v>4.979750184</v>
+        <v>4.963835532000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1682810984372329</v>
+        <v>0.1709520386185393</v>
       </c>
       <c r="T60">
-        <v>1.596339306202501</v>
+        <v>1.631150610561599</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.163155588560349</v>
+        <v>4.092593629432207</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09668989583360113</v>
+        <v>0.09655301032356443</v>
       </c>
       <c r="C61">
-        <v>21.29485336385881</v>
+        <v>21.04847438743768</v>
       </c>
       <c r="D61">
-        <v>39.5318533638588</v>
+        <v>39.63847438743768</v>
       </c>
       <c r="E61">
-        <v>-3.373000000000001</v>
+        <v>-3.020000000000003</v>
       </c>
       <c r="F61">
-        <v>20.827</v>
+        <v>21.18</v>
       </c>
       <c r="G61">
         <v>2.59</v>
@@ -6277,28 +6277,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M61">
-        <v>1.2038006</v>
+        <v>1.224204</v>
       </c>
       <c r="N61">
-        <v>3.722866066666668</v>
+        <v>3.702462666666668</v>
       </c>
       <c r="O61">
-        <v>0.8190305346666669</v>
+        <v>0.8145417866666669</v>
       </c>
       <c r="P61">
-        <v>2.903835532</v>
+        <v>2.887920880000001</v>
       </c>
       <c r="Q61">
-        <v>4.963835532000001</v>
+        <v>4.947920880000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1709520386185393</v>
+        <v>0.1737565258089111</v>
       </c>
       <c r="T61">
-        <v>1.631150610561599</v>
+        <v>1.667702480138652</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.092593629432207</v>
+        <v>4.024383735608337</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09655301032356443</v>
+        <v>0.09808142481352775</v>
       </c>
       <c r="C62">
-        <v>21.04847438743768</v>
+        <v>19.53666858155376</v>
       </c>
       <c r="D62">
-        <v>39.63847438743768</v>
+        <v>38.47966858155376</v>
       </c>
       <c r="E62">
-        <v>-3.020000000000003</v>
+        <v>-2.667000000000002</v>
       </c>
       <c r="F62">
-        <v>21.18</v>
+        <v>21.533</v>
       </c>
       <c r="G62">
         <v>2.59</v>
@@ -6359,45 +6359,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M62">
-        <v>1.224204</v>
+        <v>1.3199729</v>
       </c>
       <c r="N62">
-        <v>3.702462666666668</v>
+        <v>3.606693766666668</v>
       </c>
       <c r="O62">
-        <v>0.8145417866666669</v>
+        <v>0.7934726286666669</v>
       </c>
       <c r="P62">
-        <v>2.887920880000001</v>
+        <v>2.813221138000001</v>
       </c>
       <c r="Q62">
-        <v>4.947920880000002</v>
+        <v>4.873221138000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1737565258089111</v>
+        <v>0.1767048328551993</v>
       </c>
       <c r="T62">
-        <v>1.667702480138652</v>
+        <v>1.706128804565809</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.024383735608337</v>
+        <v>3.732399859623382</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09808142481352775</v>
+        <v>0.09797183930349107</v>
       </c>
       <c r="C63">
-        <v>19.53666858155376</v>
+        <v>19.26449406449336</v>
       </c>
       <c r="D63">
-        <v>38.47966858155376</v>
+        <v>38.56049406449336</v>
       </c>
       <c r="E63">
-        <v>-2.667000000000002</v>
+        <v>-2.314</v>
       </c>
       <c r="F63">
-        <v>21.533</v>
+        <v>21.886</v>
       </c>
       <c r="G63">
         <v>2.59</v>
@@ -6441,28 +6441,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M63">
-        <v>1.3199729</v>
+        <v>1.3416118</v>
       </c>
       <c r="N63">
-        <v>3.606693766666668</v>
+        <v>3.585054866666668</v>
       </c>
       <c r="O63">
-        <v>0.7934726286666669</v>
+        <v>0.7887120706666669</v>
       </c>
       <c r="P63">
-        <v>2.813221138000001</v>
+        <v>2.796342796000001</v>
       </c>
       <c r="Q63">
-        <v>4.873221138000002</v>
+        <v>4.856342796000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1767048328551993</v>
+        <v>0.1798083139565554</v>
       </c>
       <c r="T63">
-        <v>1.706128804565809</v>
+        <v>1.746577567120712</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.732399859623382</v>
+        <v>3.67219986188752</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09797183930349107</v>
+        <v>0.09786225379345437</v>
       </c>
       <c r="C64">
-        <v>19.26449406449336</v>
+        <v>18.99265980553272</v>
       </c>
       <c r="D64">
-        <v>38.56049406449336</v>
+        <v>38.64165980553271</v>
       </c>
       <c r="E64">
-        <v>-2.314</v>
+        <v>-1.961000000000002</v>
       </c>
       <c r="F64">
-        <v>21.886</v>
+        <v>22.239</v>
       </c>
       <c r="G64">
         <v>2.59</v>
@@ -6523,28 +6523,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M64">
-        <v>1.3416118</v>
+        <v>1.3632507</v>
       </c>
       <c r="N64">
-        <v>3.585054866666668</v>
+        <v>3.563415966666668</v>
       </c>
       <c r="O64">
-        <v>0.7887120706666669</v>
+        <v>0.7839515126666668</v>
       </c>
       <c r="P64">
-        <v>2.796342796000001</v>
+        <v>2.779464454000001</v>
       </c>
       <c r="Q64">
-        <v>4.856342796000001</v>
+        <v>4.839464454000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1798083139565554</v>
+        <v>0.1830795507931199</v>
       </c>
       <c r="T64">
-        <v>1.746577567120712</v>
+        <v>1.789212749273178</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.67219986188752</v>
+        <v>3.613910975190894</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09786225379345437</v>
+        <v>0.09775266828341769</v>
       </c>
       <c r="C65">
-        <v>18.99265980553272</v>
+        <v>18.72116795782534</v>
       </c>
       <c r="D65">
-        <v>38.64165980553271</v>
+        <v>38.72316795782534</v>
       </c>
       <c r="E65">
-        <v>-1.961000000000002</v>
+        <v>-1.608000000000001</v>
       </c>
       <c r="F65">
-        <v>22.239</v>
+        <v>22.592</v>
       </c>
       <c r="G65">
         <v>2.59</v>
@@ -6605,28 +6605,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M65">
-        <v>1.3632507</v>
+        <v>1.3848896</v>
       </c>
       <c r="N65">
-        <v>3.563415966666668</v>
+        <v>3.541777066666667</v>
       </c>
       <c r="O65">
-        <v>0.7839515126666668</v>
+        <v>0.7791909546666669</v>
       </c>
       <c r="P65">
-        <v>2.779464454000001</v>
+        <v>2.762586112000001</v>
       </c>
       <c r="Q65">
-        <v>4.839464454000001</v>
+        <v>4.822586112000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1830795507931199</v>
+        <v>0.1865325230094936</v>
       </c>
       <c r="T65">
-        <v>1.789212749273178</v>
+        <v>1.834216552656336</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.613910975190894</v>
+        <v>3.557443616203535</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09775266828341769</v>
+        <v>0.09764308277338102</v>
       </c>
       <c r="C66">
-        <v>18.72116795782534</v>
+        <v>18.45002069273009</v>
       </c>
       <c r="D66">
-        <v>38.72316795782534</v>
+        <v>38.80502069273008</v>
       </c>
       <c r="E66">
-        <v>-1.608000000000001</v>
+        <v>-1.254999999999999</v>
       </c>
       <c r="F66">
-        <v>22.592</v>
+        <v>22.945</v>
       </c>
       <c r="G66">
         <v>2.59</v>
@@ -6687,28 +6687,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M66">
-        <v>1.3848896</v>
+        <v>1.4065285</v>
       </c>
       <c r="N66">
-        <v>3.541777066666667</v>
+        <v>3.520138166666667</v>
       </c>
       <c r="O66">
-        <v>0.7791909546666669</v>
+        <v>0.7744303966666668</v>
       </c>
       <c r="P66">
-        <v>2.762586112000001</v>
+        <v>2.745707770000001</v>
       </c>
       <c r="Q66">
-        <v>4.822586112000001</v>
+        <v>4.805707770000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1865325230094936</v>
+        <v>0.1901828079239458</v>
       </c>
       <c r="T66">
-        <v>1.834216552656336</v>
+        <v>1.881792001947103</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.557443616203535</v>
+        <v>3.502713714415788</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09764308277338102</v>
+        <v>0.09897493726334433</v>
       </c>
       <c r="C67">
-        <v>18.45002069273009</v>
+        <v>17.12508459458713</v>
       </c>
       <c r="D67">
-        <v>38.80502069273008</v>
+        <v>37.83308459458712</v>
       </c>
       <c r="E67">
-        <v>-1.254999999999999</v>
+        <v>-0.902000000000001</v>
       </c>
       <c r="F67">
-        <v>22.945</v>
+        <v>23.298</v>
       </c>
       <c r="G67">
         <v>2.59</v>
@@ -6769,45 +6769,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M67">
-        <v>1.4065285</v>
+        <v>1.4934018</v>
       </c>
       <c r="N67">
-        <v>3.520138166666667</v>
+        <v>3.433264866666668</v>
       </c>
       <c r="O67">
-        <v>0.7744303966666668</v>
+        <v>0.7553182706666669</v>
       </c>
       <c r="P67">
-        <v>2.745707770000001</v>
+        <v>2.677946596000001</v>
       </c>
       <c r="Q67">
-        <v>4.805707770000001</v>
+        <v>4.737946596</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1901828079239458</v>
+        <v>0.1940478154804245</v>
       </c>
       <c r="T67">
-        <v>1.881792001947103</v>
+        <v>1.932166007078503</v>
       </c>
       <c r="U67">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.502713714415788</v>
+        <v>3.298955891620505</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09897493726334433</v>
+        <v>0.09888719175330765</v>
       </c>
       <c r="C68">
-        <v>17.12508459458713</v>
+        <v>16.83461725443169</v>
       </c>
       <c r="D68">
-        <v>37.83308459458712</v>
+        <v>37.89561725443168</v>
       </c>
       <c r="E68">
-        <v>-0.902000000000001</v>
+        <v>-0.5489999999999995</v>
       </c>
       <c r="F68">
-        <v>23.298</v>
+        <v>23.651</v>
       </c>
       <c r="G68">
         <v>2.59</v>
@@ -6851,28 +6851,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M68">
-        <v>1.4934018</v>
+        <v>1.5160291</v>
       </c>
       <c r="N68">
-        <v>3.433264866666668</v>
+        <v>3.410637566666668</v>
       </c>
       <c r="O68">
-        <v>0.7553182706666669</v>
+        <v>0.7503402646666669</v>
       </c>
       <c r="P68">
-        <v>2.677946596000001</v>
+        <v>2.660297302000001</v>
       </c>
       <c r="Q68">
-        <v>4.737946596</v>
+        <v>4.720297302000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1940478154804245</v>
+        <v>0.1981470659191141</v>
       </c>
       <c r="T68">
-        <v>1.932166007078503</v>
+        <v>1.985592982217867</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.298955891620505</v>
+        <v>3.249717743984379</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09888719175330765</v>
+        <v>0.09879944624327097</v>
       </c>
       <c r="C69">
-        <v>16.83461725443169</v>
+        <v>16.54435697153895</v>
       </c>
       <c r="D69">
-        <v>37.89561725443168</v>
+        <v>37.95835697153895</v>
       </c>
       <c r="E69">
-        <v>-0.5489999999999995</v>
+        <v>-0.195999999999998</v>
       </c>
       <c r="F69">
-        <v>23.651</v>
+        <v>24.004</v>
       </c>
       <c r="G69">
         <v>2.59</v>
@@ -6933,28 +6933,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M69">
-        <v>1.5160291</v>
+        <v>1.5386564</v>
       </c>
       <c r="N69">
-        <v>3.410637566666668</v>
+        <v>3.388010266666667</v>
       </c>
       <c r="O69">
-        <v>0.7503402646666669</v>
+        <v>0.7453622586666668</v>
       </c>
       <c r="P69">
-        <v>2.660297302000001</v>
+        <v>2.642648008000001</v>
       </c>
       <c r="Q69">
-        <v>4.720297302000001</v>
+        <v>4.702648008000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1981470659191141</v>
+        <v>0.2025025195102218</v>
       </c>
       <c r="T69">
-        <v>1.985592982217867</v>
+        <v>2.042359143303441</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.249717743984379</v>
+        <v>3.201927777161078</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09879944624327097</v>
+        <v>0.09871170073323429</v>
       </c>
       <c r="C70">
-        <v>16.54435697153895</v>
+        <v>16.25430477602202</v>
       </c>
       <c r="D70">
-        <v>37.95835697153895</v>
+        <v>38.02130477602202</v>
       </c>
       <c r="E70">
-        <v>-0.195999999999998</v>
+        <v>0.157</v>
       </c>
       <c r="F70">
-        <v>24.004</v>
+        <v>24.357</v>
       </c>
       <c r="G70">
         <v>2.59</v>
@@ -7015,28 +7015,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M70">
-        <v>1.5386564</v>
+        <v>1.5612837</v>
       </c>
       <c r="N70">
-        <v>3.388010266666667</v>
+        <v>3.365382966666667</v>
       </c>
       <c r="O70">
-        <v>0.7453622586666668</v>
+        <v>0.7403842526666669</v>
       </c>
       <c r="P70">
-        <v>2.642648008000001</v>
+        <v>2.624998714000001</v>
       </c>
       <c r="Q70">
-        <v>4.702648008000001</v>
+        <v>4.684998714000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2025025195102218</v>
+        <v>0.2071389701072074</v>
       </c>
       <c r="T70">
-        <v>2.042359143303441</v>
+        <v>2.102787637362278</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.201927777161078</v>
+        <v>3.155523026767439</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09871170073323429</v>
+        <v>0.09862395522319761</v>
       </c>
       <c r="C71">
-        <v>16.25430477602202</v>
+        <v>15.96446170483842</v>
       </c>
       <c r="D71">
-        <v>38.02130477602202</v>
+        <v>38.08446170483842</v>
       </c>
       <c r="E71">
-        <v>0.157</v>
+        <v>0.5100000000000016</v>
       </c>
       <c r="F71">
-        <v>24.357</v>
+        <v>24.71</v>
       </c>
       <c r="G71">
         <v>2.59</v>
@@ -7097,28 +7097,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M71">
-        <v>1.5612837</v>
+        <v>1.583911</v>
       </c>
       <c r="N71">
-        <v>3.365382966666667</v>
+        <v>3.342755666666668</v>
       </c>
       <c r="O71">
-        <v>0.7403842526666669</v>
+        <v>0.7354062466666669</v>
       </c>
       <c r="P71">
-        <v>2.624998714000001</v>
+        <v>2.607349420000001</v>
       </c>
       <c r="Q71">
-        <v>4.684998714000001</v>
+        <v>4.667349420000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2071389701072074</v>
+        <v>0.2120845174106587</v>
       </c>
       <c r="T71">
-        <v>2.102787637362278</v>
+        <v>2.167244697691704</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.155523026767439</v>
+        <v>3.110444126385048</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09862395522319761</v>
+        <v>0.09853620971316093</v>
       </c>
       <c r="C72">
-        <v>15.96446170483842</v>
+        <v>15.67482880184708</v>
       </c>
       <c r="D72">
-        <v>38.08446170483842</v>
+        <v>38.14782880184708</v>
       </c>
       <c r="E72">
-        <v>0.5100000000000016</v>
+        <v>0.8630000000000031</v>
       </c>
       <c r="F72">
-        <v>24.71</v>
+        <v>25.063</v>
       </c>
       <c r="G72">
         <v>2.59</v>
@@ -7179,28 +7179,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M72">
-        <v>1.583911</v>
+        <v>1.6065383</v>
       </c>
       <c r="N72">
-        <v>3.342755666666668</v>
+        <v>3.320128366666667</v>
       </c>
       <c r="O72">
-        <v>0.7354062466666669</v>
+        <v>0.7304282406666668</v>
       </c>
       <c r="P72">
-        <v>2.607349420000001</v>
+        <v>2.589700126</v>
       </c>
       <c r="Q72">
-        <v>4.667349420000001</v>
+        <v>4.649700126000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2120845174106587</v>
+        <v>0.2173711369419342</v>
       </c>
       <c r="T72">
-        <v>2.167244697691704</v>
+        <v>2.236147072526609</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.110444126385048</v>
+        <v>3.066635054182441</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09853620971316092</v>
+        <v>0.09844846420312424</v>
       </c>
       <c r="C73">
-        <v>15.67482880184711</v>
+        <v>15.3854071178659</v>
       </c>
       <c r="D73">
-        <v>38.1478288018471</v>
+        <v>38.21140711786589</v>
       </c>
       <c r="E73">
-        <v>0.862999999999996</v>
+        <v>1.215999999999998</v>
       </c>
       <c r="F73">
-        <v>25.063</v>
+        <v>25.416</v>
       </c>
       <c r="G73">
         <v>2.59</v>
@@ -7261,28 +7261,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M73">
-        <v>1.6065383</v>
+        <v>1.6291656</v>
       </c>
       <c r="N73">
-        <v>3.320128366666668</v>
+        <v>3.297501066666668</v>
       </c>
       <c r="O73">
-        <v>0.730428240666667</v>
+        <v>0.7254502346666669</v>
       </c>
       <c r="P73">
-        <v>2.589700126000001</v>
+        <v>2.572050832000001</v>
       </c>
       <c r="Q73">
-        <v>4.649700126000001</v>
+        <v>4.632050832000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2173711369419342</v>
+        <v>0.2230353721540151</v>
       </c>
       <c r="T73">
-        <v>2.236147072526608</v>
+        <v>2.309971045564005</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.066635054182442</v>
+        <v>3.02404290065213</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09844846420312424</v>
+        <v>0.1028020386930875</v>
       </c>
       <c r="C74">
-        <v>15.3854071178659</v>
+        <v>12.11398154804295</v>
       </c>
       <c r="D74">
-        <v>38.21140711786589</v>
+        <v>35.29298154804295</v>
       </c>
       <c r="E74">
-        <v>1.215999999999998</v>
+        <v>1.568999999999999</v>
       </c>
       <c r="F74">
-        <v>25.416</v>
+        <v>25.769</v>
       </c>
       <c r="G74">
         <v>2.59</v>
@@ -7343,45 +7343,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M74">
-        <v>1.6291656</v>
+        <v>1.8527911</v>
       </c>
       <c r="N74">
-        <v>3.297501066666668</v>
+        <v>3.073875566666668</v>
       </c>
       <c r="O74">
-        <v>0.7254502346666669</v>
+        <v>0.6762526246666668</v>
       </c>
       <c r="P74">
-        <v>2.572050832000001</v>
+        <v>2.397622942000001</v>
       </c>
       <c r="Q74">
-        <v>4.632050832000001</v>
+        <v>4.457622942</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2230353721540151</v>
+        <v>0.2291191803447687</v>
       </c>
       <c r="T74">
-        <v>2.309971045564005</v>
+        <v>2.389263461048616</v>
       </c>
       <c r="U74">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.22</v>
       </c>
       <c r="W74">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.02404290065213</v>
+        <v>2.659051345112068</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1028020386930875</v>
+        <v>0.1027751331830509</v>
       </c>
       <c r="C75">
-        <v>12.11398154804295</v>
+        <v>11.77764804123419</v>
       </c>
       <c r="D75">
-        <v>35.29298154804295</v>
+        <v>35.30964804123418</v>
       </c>
       <c r="E75">
-        <v>1.568999999999999</v>
+        <v>1.921999999999997</v>
       </c>
       <c r="F75">
-        <v>25.769</v>
+        <v>26.122</v>
       </c>
       <c r="G75">
         <v>2.59</v>
@@ -7425,28 +7425,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M75">
-        <v>1.8527911</v>
+        <v>1.8781718</v>
       </c>
       <c r="N75">
-        <v>3.073875566666668</v>
+        <v>3.048494866666668</v>
       </c>
       <c r="O75">
-        <v>0.6762526246666668</v>
+        <v>0.6706688706666669</v>
       </c>
       <c r="P75">
-        <v>2.397622942000001</v>
+        <v>2.377825996000001</v>
       </c>
       <c r="Q75">
-        <v>4.457622942</v>
+        <v>4.437825996000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2291191803447687</v>
+        <v>0.2356709737809648</v>
       </c>
       <c r="T75">
-        <v>2.389263461048616</v>
+        <v>2.474655293108967</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.659051345112068</v>
+        <v>2.62311821882677</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1027751331830509</v>
+        <v>0.1027482276730142</v>
       </c>
       <c r="C76">
-        <v>11.77764804123419</v>
+        <v>11.44133028278209</v>
       </c>
       <c r="D76">
-        <v>35.30964804123418</v>
+        <v>35.32633028278208</v>
       </c>
       <c r="E76">
-        <v>1.921999999999997</v>
+        <v>2.274999999999999</v>
       </c>
       <c r="F76">
-        <v>26.122</v>
+        <v>26.475</v>
       </c>
       <c r="G76">
         <v>2.59</v>
@@ -7507,28 +7507,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M76">
-        <v>1.8781718</v>
+        <v>1.9035525</v>
       </c>
       <c r="N76">
-        <v>3.048494866666668</v>
+        <v>3.023114166666668</v>
       </c>
       <c r="O76">
-        <v>0.6706688706666669</v>
+        <v>0.6650851166666669</v>
       </c>
       <c r="P76">
-        <v>2.377825996000001</v>
+        <v>2.358029050000001</v>
       </c>
       <c r="Q76">
-        <v>4.437825996000001</v>
+        <v>4.418029050000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2356709737809648</v>
+        <v>0.2427469106920567</v>
       </c>
       <c r="T76">
-        <v>2.474655293108967</v>
+        <v>2.566878471734146</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.62311821882677</v>
+        <v>2.588143309242413</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1027482276730142</v>
+        <v>0.1027213221629775</v>
       </c>
       <c r="C77">
-        <v>11.44133028278209</v>
+        <v>11.10502829501835</v>
       </c>
       <c r="D77">
-        <v>35.32633028278208</v>
+        <v>35.34302829501835</v>
       </c>
       <c r="E77">
-        <v>2.274999999999999</v>
+        <v>2.628</v>
       </c>
       <c r="F77">
-        <v>26.475</v>
+        <v>26.828</v>
       </c>
       <c r="G77">
         <v>2.59</v>
@@ -7589,28 +7589,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M77">
-        <v>1.9035525</v>
+        <v>1.9289332</v>
       </c>
       <c r="N77">
-        <v>3.023114166666668</v>
+        <v>2.997733466666667</v>
       </c>
       <c r="O77">
-        <v>0.6650851166666669</v>
+        <v>0.6595013626666668</v>
       </c>
       <c r="P77">
-        <v>2.358029050000001</v>
+        <v>2.338232104</v>
       </c>
       <c r="Q77">
-        <v>4.418029050000001</v>
+        <v>4.398232104</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2427469106920567</v>
+        <v>0.2504125090124062</v>
       </c>
       <c r="T77">
-        <v>2.566878471734146</v>
+        <v>2.666786915244757</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.588143309242413</v>
+        <v>2.554088792015539</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1027213221629775</v>
+        <v>0.1026944166529408</v>
       </c>
       <c r="C78">
-        <v>11.10502829501835</v>
+        <v>10.76874210031703</v>
       </c>
       <c r="D78">
-        <v>35.34302829501835</v>
+        <v>35.35974210031702</v>
       </c>
       <c r="E78">
-        <v>2.628</v>
+        <v>2.980999999999998</v>
       </c>
       <c r="F78">
-        <v>26.828</v>
+        <v>27.181</v>
       </c>
       <c r="G78">
         <v>2.59</v>
@@ -7671,28 +7671,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M78">
-        <v>1.9289332</v>
+        <v>1.9543139</v>
       </c>
       <c r="N78">
-        <v>2.997733466666667</v>
+        <v>2.972352766666668</v>
       </c>
       <c r="O78">
-        <v>0.6595013626666668</v>
+        <v>0.6539176086666669</v>
       </c>
       <c r="P78">
-        <v>2.338232104</v>
+        <v>2.318435158000001</v>
       </c>
       <c r="Q78">
-        <v>4.398232104</v>
+        <v>4.378435158</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2504125090124062</v>
+        <v>0.2587446810997426</v>
       </c>
       <c r="T78">
-        <v>2.666786915244757</v>
+        <v>2.77538304949542</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.554088792015539</v>
+        <v>2.520918807703649</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1026944166529408</v>
+        <v>0.1050402711429041</v>
       </c>
       <c r="C79">
-        <v>10.76874210031703</v>
+        <v>9.015532273966336</v>
       </c>
       <c r="D79">
-        <v>35.35974210031702</v>
+        <v>33.95953227396633</v>
       </c>
       <c r="E79">
-        <v>2.980999999999998</v>
+        <v>3.334</v>
       </c>
       <c r="F79">
-        <v>27.181</v>
+        <v>27.534</v>
       </c>
       <c r="G79">
         <v>2.59</v>
@@ -7753,45 +7753,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M79">
-        <v>1.9543139</v>
+        <v>2.0870772</v>
       </c>
       <c r="N79">
-        <v>2.972352766666668</v>
+        <v>2.839589466666668</v>
       </c>
       <c r="O79">
-        <v>0.6539176086666669</v>
+        <v>0.6247096826666669</v>
       </c>
       <c r="P79">
-        <v>2.318435158000001</v>
+        <v>2.214879784000001</v>
       </c>
       <c r="Q79">
-        <v>4.378435158</v>
+        <v>4.274879784000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2587446810997426</v>
+        <v>0.2678343233768369</v>
       </c>
       <c r="T79">
-        <v>2.77538304949542</v>
+        <v>2.893851559587053</v>
       </c>
       <c r="U79">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.22</v>
       </c>
       <c r="W79">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.520918807703649</v>
+        <v>2.360557945181265</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1050402711429041</v>
+        <v>0.1050437856328674</v>
       </c>
       <c r="C80">
-        <v>9.015532273966336</v>
+        <v>8.660517709332069</v>
       </c>
       <c r="D80">
-        <v>33.95953227396633</v>
+        <v>33.95751770933207</v>
       </c>
       <c r="E80">
-        <v>3.334</v>
+        <v>3.687000000000001</v>
       </c>
       <c r="F80">
-        <v>27.534</v>
+        <v>27.887</v>
       </c>
       <c r="G80">
         <v>2.59</v>
@@ -7835,28 +7835,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M80">
-        <v>2.0870772</v>
+        <v>2.1138346</v>
       </c>
       <c r="N80">
-        <v>2.839589466666668</v>
+        <v>2.812832066666668</v>
       </c>
       <c r="O80">
-        <v>0.6247096826666669</v>
+        <v>0.6188230546666669</v>
       </c>
       <c r="P80">
-        <v>2.214879784000001</v>
+        <v>2.194009012</v>
       </c>
       <c r="Q80">
-        <v>4.274879784000001</v>
+        <v>4.254009012000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2678343233768369</v>
+        <v>0.2777896458707974</v>
       </c>
       <c r="T80">
-        <v>2.893851559587053</v>
+        <v>3.023602784925508</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.360557945181265</v>
+        <v>2.330677464862514</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1050437856328674</v>
+        <v>0.1050473001228308</v>
       </c>
       <c r="C81">
-        <v>8.660517709332069</v>
+        <v>8.305503383701687</v>
       </c>
       <c r="D81">
-        <v>33.95751770933207</v>
+        <v>33.95550338370168</v>
       </c>
       <c r="E81">
-        <v>3.687000000000001</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="F81">
-        <v>27.887</v>
+        <v>28.24</v>
       </c>
       <c r="G81">
         <v>2.59</v>
@@ -7917,28 +7917,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M81">
-        <v>2.1138346</v>
+        <v>2.140592</v>
       </c>
       <c r="N81">
-        <v>2.812832066666668</v>
+        <v>2.786074666666667</v>
       </c>
       <c r="O81">
-        <v>0.6188230546666669</v>
+        <v>0.6129364266666668</v>
       </c>
       <c r="P81">
-        <v>2.194009012</v>
+        <v>2.173138240000001</v>
       </c>
       <c r="Q81">
-        <v>4.254009012000001</v>
+        <v>4.233138240000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2777896458707974</v>
+        <v>0.2887405006141538</v>
       </c>
       <c r="T81">
-        <v>3.023602784925508</v>
+        <v>3.166329132797809</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.330677464862514</v>
+        <v>2.301543996551733</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1050473001228308</v>
+        <v>0.1050508146127941</v>
       </c>
       <c r="C82">
-        <v>8.305503383701687</v>
+        <v>7.950489297032636</v>
       </c>
       <c r="D82">
-        <v>33.95550338370168</v>
+        <v>33.95348929703263</v>
       </c>
       <c r="E82">
-        <v>4.039999999999999</v>
+        <v>4.393000000000001</v>
       </c>
       <c r="F82">
-        <v>28.24</v>
+        <v>28.593</v>
       </c>
       <c r="G82">
         <v>2.59</v>
@@ -7999,28 +7999,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M82">
-        <v>2.140592</v>
+        <v>2.1673494</v>
       </c>
       <c r="N82">
-        <v>2.786074666666667</v>
+        <v>2.759317266666668</v>
       </c>
       <c r="O82">
-        <v>0.6129364266666668</v>
+        <v>0.6070497986666669</v>
       </c>
       <c r="P82">
-        <v>2.173138240000001</v>
+        <v>2.152267468000001</v>
       </c>
       <c r="Q82">
-        <v>4.233138240000001</v>
+        <v>4.212267468</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2887405006141538</v>
+        <v>0.3008440769094425</v>
       </c>
       <c r="T82">
-        <v>3.166329132797809</v>
+        <v>3.324079306761931</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.301543996551733</v>
+        <v>2.273129873137514</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1050508146127941</v>
+        <v>0.1050543291027574</v>
       </c>
       <c r="C83">
-        <v>7.950489297032636</v>
+        <v>7.595475449282429</v>
       </c>
       <c r="D83">
-        <v>33.95348929703263</v>
+        <v>33.95147544928243</v>
       </c>
       <c r="E83">
-        <v>4.393000000000001</v>
+        <v>4.746000000000002</v>
       </c>
       <c r="F83">
-        <v>28.593</v>
+        <v>28.946</v>
       </c>
       <c r="G83">
         <v>2.59</v>
@@ -8081,28 +8081,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M83">
-        <v>2.1673494</v>
+        <v>2.1941068</v>
       </c>
       <c r="N83">
-        <v>2.759317266666668</v>
+        <v>2.732559866666668</v>
       </c>
       <c r="O83">
-        <v>0.6070497986666669</v>
+        <v>0.6011631706666668</v>
       </c>
       <c r="P83">
-        <v>2.152267468000001</v>
+        <v>2.131396696000001</v>
       </c>
       <c r="Q83">
-        <v>4.212267468</v>
+        <v>4.191396696000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3008440769094425</v>
+        <v>0.3142924950153189</v>
       </c>
       <c r="T83">
-        <v>3.324079306761931</v>
+        <v>3.499357277833178</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.273129873137514</v>
+        <v>2.245408777123642</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1050543291027574</v>
+        <v>0.1050578435927207</v>
       </c>
       <c r="C84">
-        <v>7.595475449282429</v>
+        <v>7.240461840408521</v>
       </c>
       <c r="D84">
-        <v>33.95147544928243</v>
+        <v>33.94946184040852</v>
       </c>
       <c r="E84">
-        <v>4.746000000000002</v>
+        <v>5.099</v>
       </c>
       <c r="F84">
-        <v>28.946</v>
+        <v>29.299</v>
       </c>
       <c r="G84">
         <v>2.59</v>
@@ -8163,28 +8163,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M84">
-        <v>2.1941068</v>
+        <v>2.2208642</v>
       </c>
       <c r="N84">
-        <v>2.732559866666668</v>
+        <v>2.705802466666667</v>
       </c>
       <c r="O84">
-        <v>0.6011631706666668</v>
+        <v>0.5952765426666669</v>
       </c>
       <c r="P84">
-        <v>2.131396696000001</v>
+        <v>2.110525924</v>
       </c>
       <c r="Q84">
-        <v>4.191396696000001</v>
+        <v>4.170525924000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3142924950153189</v>
+        <v>0.3293230799571807</v>
       </c>
       <c r="T84">
-        <v>3.499357277833178</v>
+        <v>3.695256186677513</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.245408777123642</v>
+        <v>2.218355659326972</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1050578435927207</v>
+        <v>0.105061358082684</v>
       </c>
       <c r="C85">
-        <v>7.240461840408521</v>
+        <v>6.885448470368445</v>
       </c>
       <c r="D85">
-        <v>33.94946184040852</v>
+        <v>33.94744847036845</v>
       </c>
       <c r="E85">
-        <v>5.099</v>
+        <v>5.452000000000002</v>
       </c>
       <c r="F85">
-        <v>29.299</v>
+        <v>29.652</v>
       </c>
       <c r="G85">
         <v>2.59</v>
@@ -8245,28 +8245,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M85">
-        <v>2.2208642</v>
+        <v>2.2476216</v>
       </c>
       <c r="N85">
-        <v>2.705802466666667</v>
+        <v>2.679045066666667</v>
       </c>
       <c r="O85">
-        <v>0.5952765426666669</v>
+        <v>0.5893899146666668</v>
       </c>
       <c r="P85">
-        <v>2.110525924</v>
+        <v>2.089655152000001</v>
       </c>
       <c r="Q85">
-        <v>4.170525924000001</v>
+        <v>4.149655152000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3293230799571807</v>
+        <v>0.3462324880167753</v>
       </c>
       <c r="T85">
-        <v>3.695256186677513</v>
+        <v>3.91564245912739</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.218355659326972</v>
+        <v>2.191946663382603</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.105061358082684</v>
+        <v>0.1050648725726473</v>
       </c>
       <c r="C86">
-        <v>6.885448470368448</v>
+        <v>6.530435339119691</v>
       </c>
       <c r="D86">
-        <v>33.94744847036845</v>
+        <v>33.94543533911969</v>
       </c>
       <c r="E86">
-        <v>5.451999999999998</v>
+        <v>5.804999999999996</v>
       </c>
       <c r="F86">
-        <v>29.652</v>
+        <v>30.005</v>
       </c>
       <c r="G86">
         <v>2.59</v>
@@ -8327,28 +8327,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M86">
-        <v>2.2476216</v>
+        <v>2.274379</v>
       </c>
       <c r="N86">
-        <v>2.679045066666668</v>
+        <v>2.652287666666668</v>
       </c>
       <c r="O86">
-        <v>0.5893899146666669</v>
+        <v>0.583503286666667</v>
       </c>
       <c r="P86">
-        <v>2.089655152000001</v>
+        <v>2.068784380000001</v>
       </c>
       <c r="Q86">
-        <v>4.149655152000001</v>
+        <v>4.128784380000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3462324880167751</v>
+        <v>0.3653964838176489</v>
       </c>
       <c r="T86">
-        <v>3.915642459127387</v>
+        <v>4.165413567903913</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.191946663382603</v>
+        <v>2.166159055578102</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1050648725726473</v>
+        <v>0.1050683870626107</v>
       </c>
       <c r="C87">
-        <v>6.530435339119691</v>
+        <v>6.175422446619798</v>
       </c>
       <c r="D87">
-        <v>33.94543533911969</v>
+        <v>33.9434224466198</v>
       </c>
       <c r="E87">
-        <v>5.804999999999996</v>
+        <v>6.157999999999998</v>
       </c>
       <c r="F87">
-        <v>30.005</v>
+        <v>30.358</v>
       </c>
       <c r="G87">
         <v>2.59</v>
@@ -8409,28 +8409,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M87">
-        <v>2.274379</v>
+        <v>2.3011364</v>
       </c>
       <c r="N87">
-        <v>2.652287666666668</v>
+        <v>2.625530266666668</v>
       </c>
       <c r="O87">
-        <v>0.583503286666667</v>
+        <v>0.5776166586666669</v>
       </c>
       <c r="P87">
-        <v>2.068784380000001</v>
+        <v>2.047913608000001</v>
       </c>
       <c r="Q87">
-        <v>4.128784380000001</v>
+        <v>4.107913608</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3653964838176489</v>
+        <v>0.3872981933043618</v>
       </c>
       <c r="T87">
-        <v>4.165413567903913</v>
+        <v>4.450866263648514</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.166159055578102</v>
+        <v>2.140971159583008</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1050683870626107</v>
+        <v>0.105071901552574</v>
       </c>
       <c r="C88">
-        <v>6.175422446619798</v>
+        <v>5.820409792826268</v>
       </c>
       <c r="D88">
-        <v>33.9434224466198</v>
+        <v>33.94140979282626</v>
       </c>
       <c r="E88">
-        <v>6.157999999999998</v>
+        <v>6.510999999999999</v>
       </c>
       <c r="F88">
-        <v>30.358</v>
+        <v>30.711</v>
       </c>
       <c r="G88">
         <v>2.59</v>
@@ -8491,28 +8491,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M88">
-        <v>2.3011364</v>
+        <v>2.3278938</v>
       </c>
       <c r="N88">
-        <v>2.625530266666668</v>
+        <v>2.598772866666668</v>
       </c>
       <c r="O88">
-        <v>0.5776166586666669</v>
+        <v>0.5717300306666668</v>
       </c>
       <c r="P88">
-        <v>2.047913608000001</v>
+        <v>2.027042836000001</v>
       </c>
       <c r="Q88">
-        <v>4.107913608</v>
+        <v>4.087042836</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3872981933043618</v>
+        <v>0.4125693965582613</v>
       </c>
       <c r="T88">
-        <v>4.450866263648514</v>
+        <v>4.780234758738439</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.140971159583008</v>
+        <v>2.116362295679755</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.105071901552574</v>
+        <v>0.1050754160425373</v>
       </c>
       <c r="C89">
-        <v>5.820409792826268</v>
+        <v>5.465397377696672</v>
       </c>
       <c r="D89">
-        <v>33.94140979282626</v>
+        <v>33.93939737769666</v>
       </c>
       <c r="E89">
-        <v>6.510999999999999</v>
+        <v>6.863999999999997</v>
       </c>
       <c r="F89">
-        <v>30.711</v>
+        <v>31.064</v>
       </c>
       <c r="G89">
         <v>2.59</v>
@@ -8573,28 +8573,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M89">
-        <v>2.3278938</v>
+        <v>2.3546512</v>
       </c>
       <c r="N89">
-        <v>2.598772866666668</v>
+        <v>2.572015466666668</v>
       </c>
       <c r="O89">
-        <v>0.5717300306666668</v>
+        <v>0.565843402666667</v>
       </c>
       <c r="P89">
-        <v>2.027042836000001</v>
+        <v>2.006172064000001</v>
       </c>
       <c r="Q89">
-        <v>4.087042836</v>
+        <v>4.066172064000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4125693965582613</v>
+        <v>0.442052467021144</v>
       </c>
       <c r="T89">
-        <v>4.780234758738439</v>
+        <v>5.164498003010018</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.116362295679755</v>
+        <v>2.09231272413794</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1050754160425373</v>
+        <v>0.1050789305325006</v>
       </c>
       <c r="C90">
-        <v>5.465397377696672</v>
+        <v>5.110385201188524</v>
       </c>
       <c r="D90">
-        <v>33.93939737769666</v>
+        <v>33.93738520118853</v>
       </c>
       <c r="E90">
-        <v>6.863999999999997</v>
+        <v>7.216999999999999</v>
       </c>
       <c r="F90">
-        <v>31.064</v>
+        <v>31.417</v>
       </c>
       <c r="G90">
         <v>2.59</v>
@@ -8655,28 +8655,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M90">
-        <v>2.3546512</v>
+        <v>2.3814086</v>
       </c>
       <c r="N90">
-        <v>2.572015466666668</v>
+        <v>2.545258066666668</v>
       </c>
       <c r="O90">
-        <v>0.565843402666667</v>
+        <v>0.5599567746666669</v>
       </c>
       <c r="P90">
-        <v>2.006172064000001</v>
+        <v>1.985301292000001</v>
       </c>
       <c r="Q90">
-        <v>4.066172064000002</v>
+        <v>4.045301292000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.442052467021144</v>
+        <v>0.4768960957500055</v>
       </c>
       <c r="T90">
-        <v>5.164498003010018</v>
+        <v>5.618627291694612</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.09231272413794</v>
+        <v>2.068803592406052</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1050789305325006</v>
+        <v>0.1050824450224639</v>
       </c>
       <c r="C91">
-        <v>5.110385201188524</v>
+        <v>4.755373263259425</v>
       </c>
       <c r="D91">
-        <v>33.93738520118853</v>
+        <v>33.93537326325943</v>
       </c>
       <c r="E91">
-        <v>7.216999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="F91">
-        <v>31.417</v>
+        <v>31.77</v>
       </c>
       <c r="G91">
         <v>2.59</v>
@@ -8737,28 +8737,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M91">
-        <v>2.3814086</v>
+        <v>2.408166</v>
       </c>
       <c r="N91">
-        <v>2.545258066666668</v>
+        <v>2.518500666666668</v>
       </c>
       <c r="O91">
-        <v>0.5599567746666669</v>
+        <v>0.5540701466666669</v>
       </c>
       <c r="P91">
-        <v>1.985301292000001</v>
+        <v>1.964430520000001</v>
       </c>
       <c r="Q91">
-        <v>4.045301292000001</v>
+        <v>4.024430520000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4768960957500055</v>
+        <v>0.5187084502246392</v>
       </c>
       <c r="T91">
-        <v>5.618627291694612</v>
+        <v>6.163582438116124</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.068803592406052</v>
+        <v>2.045816885823763</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1050824450224639</v>
+        <v>0.1050859595124272</v>
       </c>
       <c r="C92">
-        <v>4.755373263259425</v>
+        <v>4.400361563866916</v>
       </c>
       <c r="D92">
-        <v>33.93537326325943</v>
+        <v>33.93336156386691</v>
       </c>
       <c r="E92">
-        <v>7.57</v>
+        <v>7.922999999999998</v>
       </c>
       <c r="F92">
-        <v>31.77</v>
+        <v>32.123</v>
       </c>
       <c r="G92">
         <v>2.59</v>
@@ -8819,28 +8819,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M92">
-        <v>2.408166</v>
+        <v>2.4349234</v>
       </c>
       <c r="N92">
-        <v>2.518500666666668</v>
+        <v>2.491743266666667</v>
       </c>
       <c r="O92">
-        <v>0.5540701466666669</v>
+        <v>0.5481835186666668</v>
       </c>
       <c r="P92">
-        <v>1.964430520000001</v>
+        <v>1.943559748000001</v>
       </c>
       <c r="Q92">
-        <v>4.024430520000001</v>
+        <v>4.003559748000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5187084502246392</v>
+        <v>0.5698124390269694</v>
       </c>
       <c r="T92">
-        <v>6.163582438116124</v>
+        <v>6.829638728186862</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.045816885823763</v>
+        <v>2.023335381583941</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1050859595124272</v>
+        <v>0.1050894740023905</v>
       </c>
       <c r="C93">
-        <v>4.400361563866916</v>
+        <v>4.045350102968598</v>
       </c>
       <c r="D93">
-        <v>33.93336156386691</v>
+        <v>33.9313501029686</v>
       </c>
       <c r="E93">
-        <v>7.922999999999998</v>
+        <v>8.276</v>
       </c>
       <c r="F93">
-        <v>32.123</v>
+        <v>32.476</v>
       </c>
       <c r="G93">
         <v>2.59</v>
@@ -8901,28 +8901,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M93">
-        <v>2.4349234</v>
+        <v>2.4616808</v>
       </c>
       <c r="N93">
-        <v>2.491743266666667</v>
+        <v>2.464985866666667</v>
       </c>
       <c r="O93">
-        <v>0.5481835186666668</v>
+        <v>0.5422968906666669</v>
       </c>
       <c r="P93">
-        <v>1.943559748000001</v>
+        <v>1.922688976</v>
       </c>
       <c r="Q93">
-        <v>4.003559748000001</v>
+        <v>3.982688976</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5698124390269694</v>
+        <v>0.6336924250298821</v>
       </c>
       <c r="T93">
-        <v>6.829638728186862</v>
+        <v>7.662209090775284</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.023335381583941</v>
+        <v>2.001342605697159</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1050894740023905</v>
+        <v>0.1153936684923538</v>
       </c>
       <c r="C94">
-        <v>4.045350102968598</v>
+        <v>-1.331601620548295</v>
       </c>
       <c r="D94">
-        <v>33.9313501029686</v>
+        <v>28.90739837945171</v>
       </c>
       <c r="E94">
-        <v>8.276</v>
+        <v>8.629000000000001</v>
       </c>
       <c r="F94">
-        <v>32.476</v>
+        <v>32.829</v>
       </c>
       <c r="G94">
         <v>2.59</v>
@@ -8983,45 +8983,45 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M94">
-        <v>2.4616808</v>
+        <v>2.95461</v>
       </c>
       <c r="N94">
-        <v>2.464985866666667</v>
+        <v>1.972056666666668</v>
       </c>
       <c r="O94">
-        <v>0.5422968906666669</v>
+        <v>0.4338524666666669</v>
       </c>
       <c r="P94">
-        <v>1.922688976</v>
+        <v>1.538204200000001</v>
       </c>
       <c r="Q94">
-        <v>3.982688976</v>
+        <v>3.598204200000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6336924250298821</v>
+        <v>0.7158238356050555</v>
       </c>
       <c r="T94">
-        <v>7.662209090775284</v>
+        <v>8.732656699817539</v>
       </c>
       <c r="U94">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V94">
         <v>0.22</v>
       </c>
       <c r="W94">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.001342605697159</v>
+        <v>1.667450752101519</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1153936684923538</v>
+        <v>0.1155079429823172</v>
       </c>
       <c r="C95">
-        <v>-1.331601620548295</v>
+        <v>-1.731990455516737</v>
       </c>
       <c r="D95">
-        <v>28.90739837945171</v>
+        <v>28.86000954448327</v>
       </c>
       <c r="E95">
-        <v>8.629000000000001</v>
+        <v>8.982000000000003</v>
       </c>
       <c r="F95">
-        <v>32.829</v>
+        <v>33.182</v>
       </c>
       <c r="G95">
         <v>2.59</v>
@@ -9065,28 +9065,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M95">
-        <v>2.95461</v>
+        <v>2.98638</v>
       </c>
       <c r="N95">
-        <v>1.972056666666668</v>
+        <v>1.940286666666668</v>
       </c>
       <c r="O95">
-        <v>0.4338524666666669</v>
+        <v>0.4268630666666669</v>
       </c>
       <c r="P95">
-        <v>1.538204200000001</v>
+        <v>1.513423600000001</v>
       </c>
       <c r="Q95">
-        <v>3.598204200000001</v>
+        <v>3.573423600000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7158238356050555</v>
+        <v>0.8253323830386203</v>
       </c>
       <c r="T95">
-        <v>8.732656699817539</v>
+        <v>10.15992017854055</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.667450752101519</v>
+        <v>1.649711914313205</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1155079429823172</v>
+        <v>0.1156222174722805</v>
       </c>
       <c r="C96">
-        <v>-1.731990455516737</v>
+        <v>-2.132224172669037</v>
       </c>
       <c r="D96">
-        <v>28.86000954448327</v>
+        <v>28.81277582733096</v>
       </c>
       <c r="E96">
-        <v>8.982000000000003</v>
+        <v>9.334999999999997</v>
       </c>
       <c r="F96">
-        <v>33.182</v>
+        <v>33.535</v>
       </c>
       <c r="G96">
         <v>2.59</v>
@@ -9147,28 +9147,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M96">
-        <v>2.98638</v>
+        <v>3.018149999999999</v>
       </c>
       <c r="N96">
-        <v>1.940286666666668</v>
+        <v>1.908516666666668</v>
       </c>
       <c r="O96">
-        <v>0.4268630666666669</v>
+        <v>0.419873666666667</v>
       </c>
       <c r="P96">
-        <v>1.513423600000001</v>
+        <v>1.488643000000001</v>
       </c>
       <c r="Q96">
-        <v>3.573423600000001</v>
+        <v>3.548643000000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8253323830386203</v>
+        <v>0.9786443494456111</v>
       </c>
       <c r="T96">
-        <v>10.15992017854055</v>
+        <v>12.15808904875277</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.649711914313205</v>
+        <v>1.632346525741487</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1156222174722805</v>
+        <v>0.1157364919622438</v>
       </c>
       <c r="C97">
-        <v>-2.132224172669037</v>
+        <v>-2.532303532381182</v>
       </c>
       <c r="D97">
-        <v>28.81277582733096</v>
+        <v>28.76569646761882</v>
       </c>
       <c r="E97">
-        <v>9.334999999999997</v>
+        <v>9.687999999999999</v>
       </c>
       <c r="F97">
-        <v>33.535</v>
+        <v>33.888</v>
       </c>
       <c r="G97">
         <v>2.59</v>
@@ -9229,28 +9229,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M97">
-        <v>3.018149999999999</v>
+        <v>3.04992</v>
       </c>
       <c r="N97">
-        <v>1.908516666666668</v>
+        <v>1.876746666666668</v>
       </c>
       <c r="O97">
-        <v>0.419873666666667</v>
+        <v>0.4128842666666669</v>
       </c>
       <c r="P97">
-        <v>1.488643000000001</v>
+        <v>1.463862400000001</v>
       </c>
       <c r="Q97">
-        <v>3.548643000000001</v>
+        <v>3.523862400000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9786443494456111</v>
+        <v>1.208612299056097</v>
       </c>
       <c r="T97">
-        <v>12.15808904875277</v>
+        <v>15.15534235407109</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.632346525741487</v>
+        <v>1.615342916098346</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1157364919622438</v>
+        <v>0.1158507664522071</v>
       </c>
       <c r="C98">
-        <v>-2.532303532381182</v>
+        <v>-2.932229290067493</v>
       </c>
       <c r="D98">
-        <v>28.76569646761882</v>
+        <v>28.71877070993251</v>
       </c>
       <c r="E98">
-        <v>9.687999999999999</v>
+        <v>10.041</v>
       </c>
       <c r="F98">
-        <v>33.888</v>
+        <v>34.241</v>
       </c>
       <c r="G98">
         <v>2.59</v>
@@ -9311,28 +9311,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M98">
-        <v>3.04992</v>
+        <v>3.08169</v>
       </c>
       <c r="N98">
-        <v>1.876746666666668</v>
+        <v>1.844976666666668</v>
       </c>
       <c r="O98">
-        <v>0.4128842666666669</v>
+        <v>0.4058948666666669</v>
       </c>
       <c r="P98">
-        <v>1.463862400000001</v>
+        <v>1.439081800000001</v>
       </c>
       <c r="Q98">
-        <v>3.523862400000001</v>
+        <v>3.499081800000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.208612299056094</v>
+        <v>1.59189221507357</v>
       </c>
       <c r="T98">
-        <v>15.15534235407105</v>
+        <v>20.15076452960157</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.615342916098346</v>
+        <v>1.598689896344755</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1158507664522071</v>
+        <v>0.1159650409421704</v>
       </c>
       <c r="C99">
-        <v>-2.932229290067493</v>
+        <v>-3.33200219622108</v>
       </c>
       <c r="D99">
-        <v>28.71877070993251</v>
+        <v>28.67199780377891</v>
       </c>
       <c r="E99">
-        <v>10.041</v>
+        <v>10.39399999999999</v>
       </c>
       <c r="F99">
-        <v>34.241</v>
+        <v>34.59399999999999</v>
       </c>
       <c r="G99">
         <v>2.59</v>
@@ -9393,28 +9393,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M99">
-        <v>3.08169</v>
+        <v>3.113459999999999</v>
       </c>
       <c r="N99">
-        <v>1.844976666666668</v>
+        <v>1.813206666666668</v>
       </c>
       <c r="O99">
-        <v>0.4058948666666669</v>
+        <v>0.398905466666667</v>
       </c>
       <c r="P99">
-        <v>1.439081800000001</v>
+        <v>1.414301200000001</v>
       </c>
       <c r="Q99">
-        <v>3.499081800000001</v>
+        <v>3.474301200000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.59189221507357</v>
+        <v>2.35845204710852</v>
       </c>
       <c r="T99">
-        <v>20.15076452960157</v>
+        <v>30.14160888066261</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.598689896344755</v>
+        <v>1.582376734137156</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1159650409421704</v>
+        <v>0.1160793154321338</v>
       </c>
       <c r="C100">
-        <v>-3.33200219622108</v>
+        <v>-3.731622996453829</v>
       </c>
       <c r="D100">
-        <v>28.67199780377891</v>
+        <v>28.62537700354617</v>
       </c>
       <c r="E100">
-        <v>10.39399999999999</v>
+        <v>10.747</v>
       </c>
       <c r="F100">
-        <v>34.59399999999999</v>
+        <v>34.947</v>
       </c>
       <c r="G100">
         <v>2.59</v>
@@ -9475,28 +9475,28 @@
         <v>4.926666666666668</v>
       </c>
       <c r="M100">
-        <v>3.113459999999999</v>
+        <v>3.145229999999999</v>
       </c>
       <c r="N100">
-        <v>1.813206666666668</v>
+        <v>1.781436666666668</v>
       </c>
       <c r="O100">
-        <v>0.398905466666667</v>
+        <v>0.3919160666666671</v>
       </c>
       <c r="P100">
-        <v>1.414301200000001</v>
+        <v>1.389520600000001</v>
       </c>
       <c r="Q100">
-        <v>3.474301200000001</v>
+        <v>3.449520600000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.35845204710852</v>
+        <v>4.658131543213372</v>
       </c>
       <c r="T100">
-        <v>30.14160888066261</v>
+        <v>60.11414193384573</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.582376734137156</v>
+        <v>1.566393130762033</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1160793154321338</v>
-      </c>
-      <c r="C101">
-        <v>-3.731622996453829</v>
-      </c>
-      <c r="D101">
-        <v>28.62537700354617</v>
-      </c>
-      <c r="E101">
-        <v>10.747</v>
-      </c>
-      <c r="F101">
-        <v>34.947</v>
-      </c>
-      <c r="G101">
-        <v>2.59</v>
-      </c>
-      <c r="H101">
-        <v>11.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6.986666666666667</v>
-      </c>
-      <c r="K101">
-        <v>2.06</v>
-      </c>
-      <c r="L101">
-        <v>4.926666666666668</v>
-      </c>
-      <c r="M101">
-        <v>3.145229999999999</v>
-      </c>
-      <c r="N101">
-        <v>1.781436666666668</v>
-      </c>
-      <c r="O101">
-        <v>0.3919160666666671</v>
-      </c>
-      <c r="P101">
-        <v>1.389520600000001</v>
-      </c>
-      <c r="Q101">
-        <v>3.449520600000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.658131543213372</v>
-      </c>
-      <c r="T101">
-        <v>60.11414193384573</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.0702</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.566393130762033</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
